--- a/docs/team_contribution_tracker.xlsx
+++ b/docs/team_contribution_tracker.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Team Member</t>
   </si>
@@ -43,6 +43,9 @@
     <t>Oct 18 - Local Backend</t>
   </si>
   <si>
+    <t>Oct 25 - API</t>
+  </si>
+  <si>
     <t>Ebad</t>
   </si>
   <si>
@@ -56,6 +59,12 @@
   </si>
   <si>
     <t>Breanna</t>
+  </si>
+  <si>
+    <t>Please note: Grading is currently lenient regarding direct Git commit attribution. I count co-authored commits, verbal contributions, and local collaboration on an assignment as valid contributions. Since a lot of our collaboration happens locally, and team members sometimes share devices when coding, I wasn't able to assess individual contributions based on Git commits alone.</t>
+  </si>
+  <si>
+    <t>FOR MEMBERS: Moving forward, there will be more emphasis on direct git commits. So please make commits from your personal device when possible</t>
   </si>
 </sst>
 </file>
@@ -108,7 +117,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -137,6 +146,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF6F6F7"/>
         <bgColor rgb="FFF6F6F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1C232"/>
+        <bgColor rgb="FFF1C232"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -174,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -194,8 +215,14 @@
     <xf borderId="2" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="2" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="2" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="2" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
@@ -205,6 +232,15 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -509,7 +545,9 @@
       <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4"/>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
       <c r="N1" s="4"/>
@@ -528,36 +566,38 @@
     </row>
     <row r="2" ht="24.0" customHeight="1">
       <c r="A2" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="6">
         <v>100.0</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="7">
         <v>100.0</v>
       </c>
-      <c r="D2" s="6">
-        <v>100.0</v>
+      <c r="D2" s="7">
+        <v>95.0</v>
       </c>
-      <c r="E2" s="6">
-        <v>100.0</v>
+      <c r="E2" s="7">
+        <v>84.0</v>
       </c>
-      <c r="F2" s="6">
-        <v>100.0</v>
+      <c r="F2" s="7">
+        <v>95.0</v>
       </c>
-      <c r="G2" s="6">
-        <v>100.0</v>
+      <c r="G2" s="7">
+        <v>92.0</v>
       </c>
-      <c r="H2" s="6">
-        <v>100.0</v>
+      <c r="H2" s="7">
+        <v>94.0</v>
       </c>
-      <c r="I2" s="6">
-        <v>100.0</v>
+      <c r="I2" s="7">
+        <v>88.0</v>
       </c>
       <c r="J2" s="6">
         <v>100.0</v>
       </c>
-      <c r="K2" s="4"/>
+      <c r="K2" s="6">
+        <v>100.0</v>
+      </c>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
       <c r="N2" s="4"/>
@@ -576,36 +616,38 @@
     </row>
     <row r="3" ht="24.0" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="8">
         <v>100.0</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="9">
+        <v>98.0</v>
+      </c>
+      <c r="D3" s="9">
         <v>100.0</v>
       </c>
-      <c r="D3" s="7">
+      <c r="E3" s="9">
+        <v>98.0</v>
+      </c>
+      <c r="F3" s="9">
+        <v>97.0</v>
+      </c>
+      <c r="G3" s="8">
         <v>100.0</v>
       </c>
-      <c r="E3" s="7">
-        <v>100.0</v>
+      <c r="H3" s="9">
+        <v>94.0</v>
       </c>
-      <c r="F3" s="7">
-        <v>100.0</v>
+      <c r="I3" s="9">
+        <v>96.0</v>
       </c>
-      <c r="G3" s="7">
-        <v>100.0</v>
+      <c r="J3" s="9">
+        <v>87.0</v>
       </c>
-      <c r="H3" s="7">
-        <v>100.0</v>
+      <c r="K3" s="7">
+        <v>99.0</v>
       </c>
-      <c r="I3" s="7">
-        <v>100.0</v>
-      </c>
-      <c r="J3" s="7">
-        <v>100.0</v>
-      </c>
-      <c r="K3" s="4"/>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
@@ -624,36 +666,38 @@
     </row>
     <row r="4" ht="24.0" customHeight="1">
       <c r="A4" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="7">
         <v>100.0</v>
       </c>
-      <c r="C4" s="6">
-        <v>100.0</v>
+      <c r="C4" s="7">
+        <v>95.0</v>
       </c>
-      <c r="D4" s="6">
-        <v>100.0</v>
+      <c r="D4" s="7">
+        <v>98.0</v>
       </c>
-      <c r="E4" s="6">
-        <v>100.0</v>
+      <c r="E4" s="7">
+        <v>90.0</v>
       </c>
-      <c r="F4" s="6">
-        <v>100.0</v>
+      <c r="F4" s="7">
+        <v>94.0</v>
       </c>
-      <c r="G4" s="6">
-        <v>100.0</v>
+      <c r="G4" s="7">
+        <v>90.0</v>
       </c>
-      <c r="H4" s="6">
-        <v>100.0</v>
+      <c r="H4" s="7">
+        <v>98.0</v>
       </c>
-      <c r="I4" s="6">
-        <v>100.0</v>
+      <c r="I4" s="7">
+        <v>89.0</v>
       </c>
-      <c r="J4" s="6">
-        <v>100.0</v>
+      <c r="J4" s="7">
+        <v>84.0</v>
       </c>
-      <c r="K4" s="4"/>
+      <c r="K4" s="7">
+        <v>95.0</v>
+      </c>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
@@ -672,36 +716,38 @@
     </row>
     <row r="5" ht="24.0" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="9">
         <v>100.0</v>
       </c>
-      <c r="C5" s="7">
-        <v>100.0</v>
+      <c r="C5" s="9">
+        <v>84.0</v>
       </c>
-      <c r="D5" s="7">
-        <v>100.0</v>
+      <c r="D5" s="9">
+        <v>95.0</v>
       </c>
-      <c r="E5" s="7">
-        <v>100.0</v>
+      <c r="E5" s="9">
+        <v>92.0</v>
       </c>
-      <c r="F5" s="7">
-        <v>100.0</v>
+      <c r="F5" s="9">
+        <v>92.0</v>
       </c>
-      <c r="G5" s="7">
-        <v>100.0</v>
+      <c r="G5" s="9">
+        <v>92.0</v>
       </c>
-      <c r="H5" s="7">
-        <v>100.0</v>
+      <c r="H5" s="9">
+        <v>95.0</v>
       </c>
-      <c r="I5" s="7">
-        <v>100.0</v>
+      <c r="I5" s="9">
+        <v>86.0</v>
       </c>
-      <c r="J5" s="7">
-        <v>100.0</v>
+      <c r="J5" s="9">
+        <v>80.0</v>
       </c>
-      <c r="K5" s="4"/>
+      <c r="K5" s="7">
+        <v>94.0</v>
+      </c>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
@@ -720,36 +766,38 @@
     </row>
     <row r="6" ht="24.0" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <v>100.0</v>
       </c>
-      <c r="C6" s="6">
-        <v>100.0</v>
+      <c r="C6" s="7">
+        <v>93.0</v>
       </c>
       <c r="D6" s="6">
         <v>100.0</v>
       </c>
-      <c r="E6" s="6">
-        <v>100.0</v>
+      <c r="E6" s="7">
+        <v>97.0</v>
       </c>
-      <c r="F6" s="6">
-        <v>100.0</v>
+      <c r="F6" s="7">
+        <v>95.0</v>
       </c>
-      <c r="G6" s="6">
-        <v>100.0</v>
+      <c r="G6" s="7">
+        <v>94.0</v>
       </c>
-      <c r="H6" s="6">
-        <v>100.0</v>
+      <c r="H6" s="7">
+        <v>93.0</v>
       </c>
-      <c r="I6" s="6">
-        <v>100.0</v>
+      <c r="I6" s="7">
+        <v>94.0</v>
       </c>
-      <c r="J6" s="6">
-        <v>100.0</v>
+      <c r="J6" s="7">
+        <v>83.0</v>
       </c>
-      <c r="K6" s="4"/>
+      <c r="K6" s="7">
+        <v>91.0</v>
+      </c>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
@@ -767,14 +815,14 @@
       <c r="Z6" s="4"/>
     </row>
     <row r="7">
-      <c r="A7" s="8"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
+      <c r="A7" s="10"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
@@ -795,14 +843,14 @@
       <c r="Z7" s="4"/>
     </row>
     <row r="8">
-      <c r="A8" s="10"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
+      <c r="A8" s="12"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
@@ -823,14 +871,14 @@
       <c r="Z8" s="4"/>
     </row>
     <row r="9">
-      <c r="A9" s="8"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
+      <c r="A9" s="13"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
@@ -851,14 +899,16 @@
       <c r="Z9" s="4"/>
     </row>
     <row r="10">
-      <c r="A10" s="8"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
+      <c r="A10" s="10"/>
+      <c r="B10" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
@@ -879,14 +929,14 @@
       <c r="Z10" s="4"/>
     </row>
     <row r="11">
-      <c r="A11" s="8"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
+      <c r="A11" s="10"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
@@ -907,14 +957,14 @@
       <c r="Z11" s="4"/>
     </row>
     <row r="12">
-      <c r="A12" s="8"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
+      <c r="A12" s="10"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
@@ -935,14 +985,14 @@
       <c r="Z12" s="4"/>
     </row>
     <row r="13">
-      <c r="A13" s="8"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
+      <c r="A13" s="10"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
@@ -963,14 +1013,14 @@
       <c r="Z13" s="4"/>
     </row>
     <row r="14">
-      <c r="A14" s="8"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
+      <c r="A14" s="10"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
@@ -991,14 +1041,14 @@
       <c r="Z14" s="4"/>
     </row>
     <row r="15">
-      <c r="A15" s="8"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
+      <c r="A15" s="10"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
@@ -1019,14 +1069,14 @@
       <c r="Z15" s="4"/>
     </row>
     <row r="16">
-      <c r="A16" s="8"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
+      <c r="A16" s="10"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
@@ -1047,14 +1097,14 @@
       <c r="Z16" s="4"/>
     </row>
     <row r="17">
-      <c r="A17" s="8"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
+      <c r="A17" s="10"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
@@ -1075,14 +1125,14 @@
       <c r="Z17" s="4"/>
     </row>
     <row r="18">
-      <c r="A18" s="8"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
+      <c r="A18" s="10"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
@@ -1103,14 +1153,14 @@
       <c r="Z18" s="4"/>
     </row>
     <row r="19">
-      <c r="A19" s="8"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
+      <c r="A19" s="10"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
@@ -1131,14 +1181,14 @@
       <c r="Z19" s="4"/>
     </row>
     <row r="20">
-      <c r="A20" s="8"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
+      <c r="A20" s="10"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
@@ -1159,14 +1209,14 @@
       <c r="Z20" s="4"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="8"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
+      <c r="A21" s="10"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
@@ -1187,14 +1237,14 @@
       <c r="Z21" s="4"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="8"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
+      <c r="A22" s="10"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
@@ -1215,14 +1265,14 @@
       <c r="Z22" s="4"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="8"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
+      <c r="A23" s="10"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
@@ -1243,14 +1293,14 @@
       <c r="Z23" s="4"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="8"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
+      <c r="A24" s="10"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
@@ -1271,14 +1321,14 @@
       <c r="Z24" s="4"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="8"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
+      <c r="A25" s="10"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
@@ -1299,14 +1349,14 @@
       <c r="Z25" s="4"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="8"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
+      <c r="A26" s="10"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
@@ -1327,14 +1377,14 @@
       <c r="Z26" s="4"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="8"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
+      <c r="A27" s="10"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
@@ -1355,14 +1405,14 @@
       <c r="Z27" s="4"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="8"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
+      <c r="A28" s="10"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
@@ -1383,14 +1433,14 @@
       <c r="Z28" s="4"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="8"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
+      <c r="A29" s="10"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
@@ -1411,14 +1461,14 @@
       <c r="Z29" s="4"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="8"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
+      <c r="A30" s="10"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
       <c r="K30" s="4"/>
@@ -1439,14 +1489,14 @@
       <c r="Z30" s="4"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="8"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
+      <c r="A31" s="10"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
       <c r="I31" s="4"/>
       <c r="J31" s="4"/>
       <c r="K31" s="4"/>
@@ -1467,14 +1517,14 @@
       <c r="Z31" s="4"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="8"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
+      <c r="A32" s="10"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
       <c r="K32" s="4"/>
@@ -1495,14 +1545,14 @@
       <c r="Z32" s="4"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="8"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
+      <c r="A33" s="10"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
       <c r="K33" s="4"/>
@@ -1523,14 +1573,14 @@
       <c r="Z33" s="4"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="8"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
+      <c r="A34" s="10"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
       <c r="K34" s="4"/>
@@ -1551,14 +1601,14 @@
       <c r="Z34" s="4"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="8"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
+      <c r="A35" s="10"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
@@ -1579,14 +1629,14 @@
       <c r="Z35" s="4"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="8"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
+      <c r="A36" s="10"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
@@ -1607,14 +1657,14 @@
       <c r="Z36" s="4"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="8"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
+      <c r="A37" s="10"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
       <c r="I37" s="4"/>
       <c r="J37" s="4"/>
       <c r="K37" s="4"/>
@@ -1635,14 +1685,14 @@
       <c r="Z37" s="4"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="8"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
+      <c r="A38" s="10"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
       <c r="K38" s="4"/>
@@ -1663,14 +1713,14 @@
       <c r="Z38" s="4"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="8"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
+      <c r="A39" s="10"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
       <c r="K39" s="4"/>
@@ -1691,14 +1741,14 @@
       <c r="Z39" s="4"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="8"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
+      <c r="A40" s="10"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
       <c r="K40" s="4"/>
@@ -1719,14 +1769,14 @@
       <c r="Z40" s="4"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="8"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
+      <c r="A41" s="10"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
       <c r="I41" s="4"/>
       <c r="J41" s="4"/>
       <c r="K41" s="4"/>
@@ -1747,14 +1797,14 @@
       <c r="Z41" s="4"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="8"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
+      <c r="A42" s="10"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="11"/>
+      <c r="H42" s="11"/>
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
       <c r="K42" s="4"/>
@@ -1775,14 +1825,14 @@
       <c r="Z42" s="4"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="8"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
+      <c r="A43" s="10"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
       <c r="K43" s="4"/>
@@ -1803,14 +1853,14 @@
       <c r="Z43" s="4"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="8"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
+      <c r="A44" s="10"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="11"/>
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
       <c r="K44" s="4"/>
@@ -1831,14 +1881,14 @@
       <c r="Z44" s="4"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="8"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
+      <c r="A45" s="10"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="11"/>
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
       <c r="K45" s="4"/>
@@ -1859,14 +1909,14 @@
       <c r="Z45" s="4"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="8"/>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-      <c r="H46" s="9"/>
+      <c r="A46" s="10"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
       <c r="K46" s="4"/>
@@ -1887,14 +1937,14 @@
       <c r="Z46" s="4"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="8"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="9"/>
-      <c r="H47" s="9"/>
+      <c r="A47" s="10"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="11"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="11"/>
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
       <c r="K47" s="4"/>
@@ -1915,14 +1965,14 @@
       <c r="Z47" s="4"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="8"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="9"/>
-      <c r="H48" s="9"/>
+      <c r="A48" s="10"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="11"/>
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
       <c r="K48" s="4"/>
@@ -1943,14 +1993,14 @@
       <c r="Z48" s="4"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="8"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="9"/>
-      <c r="H49" s="9"/>
+      <c r="A49" s="10"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="11"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="11"/>
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
       <c r="K49" s="4"/>
@@ -1971,14 +2021,14 @@
       <c r="Z49" s="4"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="8"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="9"/>
-      <c r="H50" s="9"/>
+      <c r="A50" s="10"/>
+      <c r="B50" s="11"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="11"/>
       <c r="I50" s="4"/>
       <c r="J50" s="4"/>
       <c r="K50" s="4"/>
@@ -1999,14 +2049,14 @@
       <c r="Z50" s="4"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="8"/>
-      <c r="B51" s="9"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="9"/>
-      <c r="H51" s="9"/>
+      <c r="A51" s="10"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="11"/>
       <c r="I51" s="4"/>
       <c r="J51" s="4"/>
       <c r="K51" s="4"/>
@@ -2027,14 +2077,14 @@
       <c r="Z51" s="4"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="8"/>
-      <c r="B52" s="9"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="9"/>
-      <c r="H52" s="9"/>
+      <c r="A52" s="10"/>
+      <c r="B52" s="11"/>
+      <c r="C52" s="11"/>
+      <c r="D52" s="11"/>
+      <c r="E52" s="11"/>
+      <c r="F52" s="11"/>
+      <c r="G52" s="11"/>
+      <c r="H52" s="11"/>
       <c r="I52" s="4"/>
       <c r="J52" s="4"/>
       <c r="K52" s="4"/>
@@ -2055,14 +2105,14 @@
       <c r="Z52" s="4"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="8"/>
-      <c r="B53" s="9"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="9"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="9"/>
-      <c r="H53" s="9"/>
+      <c r="A53" s="10"/>
+      <c r="B53" s="11"/>
+      <c r="C53" s="11"/>
+      <c r="D53" s="11"/>
+      <c r="E53" s="11"/>
+      <c r="F53" s="11"/>
+      <c r="G53" s="11"/>
+      <c r="H53" s="11"/>
       <c r="I53" s="4"/>
       <c r="J53" s="4"/>
       <c r="K53" s="4"/>
@@ -2083,14 +2133,14 @@
       <c r="Z53" s="4"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="8"/>
-      <c r="B54" s="9"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="9"/>
-      <c r="H54" s="9"/>
+      <c r="A54" s="10"/>
+      <c r="B54" s="11"/>
+      <c r="C54" s="11"/>
+      <c r="D54" s="11"/>
+      <c r="E54" s="11"/>
+      <c r="F54" s="11"/>
+      <c r="G54" s="11"/>
+      <c r="H54" s="11"/>
       <c r="I54" s="4"/>
       <c r="J54" s="4"/>
       <c r="K54" s="4"/>
@@ -2111,14 +2161,14 @@
       <c r="Z54" s="4"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="8"/>
-      <c r="B55" s="9"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="9"/>
-      <c r="H55" s="9"/>
+      <c r="A55" s="10"/>
+      <c r="B55" s="11"/>
+      <c r="C55" s="11"/>
+      <c r="D55" s="11"/>
+      <c r="E55" s="11"/>
+      <c r="F55" s="11"/>
+      <c r="G55" s="11"/>
+      <c r="H55" s="11"/>
       <c r="I55" s="4"/>
       <c r="J55" s="4"/>
       <c r="K55" s="4"/>
@@ -2139,14 +2189,14 @@
       <c r="Z55" s="4"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="8"/>
-      <c r="B56" s="9"/>
-      <c r="C56" s="9"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="9"/>
-      <c r="H56" s="9"/>
+      <c r="A56" s="10"/>
+      <c r="B56" s="11"/>
+      <c r="C56" s="11"/>
+      <c r="D56" s="11"/>
+      <c r="E56" s="11"/>
+      <c r="F56" s="11"/>
+      <c r="G56" s="11"/>
+      <c r="H56" s="11"/>
       <c r="I56" s="4"/>
       <c r="J56" s="4"/>
       <c r="K56" s="4"/>
@@ -2167,14 +2217,14 @@
       <c r="Z56" s="4"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="8"/>
-      <c r="B57" s="9"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9"/>
-      <c r="G57" s="9"/>
-      <c r="H57" s="9"/>
+      <c r="A57" s="10"/>
+      <c r="B57" s="11"/>
+      <c r="C57" s="11"/>
+      <c r="D57" s="11"/>
+      <c r="E57" s="11"/>
+      <c r="F57" s="11"/>
+      <c r="G57" s="11"/>
+      <c r="H57" s="11"/>
       <c r="I57" s="4"/>
       <c r="J57" s="4"/>
       <c r="K57" s="4"/>
@@ -2195,14 +2245,14 @@
       <c r="Z57" s="4"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="8"/>
-      <c r="B58" s="9"/>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9"/>
-      <c r="G58" s="9"/>
-      <c r="H58" s="9"/>
+      <c r="A58" s="10"/>
+      <c r="B58" s="11"/>
+      <c r="C58" s="11"/>
+      <c r="D58" s="11"/>
+      <c r="E58" s="11"/>
+      <c r="F58" s="11"/>
+      <c r="G58" s="11"/>
+      <c r="H58" s="11"/>
       <c r="I58" s="4"/>
       <c r="J58" s="4"/>
       <c r="K58" s="4"/>
@@ -2223,14 +2273,14 @@
       <c r="Z58" s="4"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="8"/>
-      <c r="B59" s="9"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
-      <c r="F59" s="9"/>
-      <c r="G59" s="9"/>
-      <c r="H59" s="9"/>
+      <c r="A59" s="10"/>
+      <c r="B59" s="11"/>
+      <c r="C59" s="11"/>
+      <c r="D59" s="11"/>
+      <c r="E59" s="11"/>
+      <c r="F59" s="11"/>
+      <c r="G59" s="11"/>
+      <c r="H59" s="11"/>
       <c r="I59" s="4"/>
       <c r="J59" s="4"/>
       <c r="K59" s="4"/>
@@ -2251,14 +2301,14 @@
       <c r="Z59" s="4"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="8"/>
-      <c r="B60" s="9"/>
-      <c r="C60" s="9"/>
-      <c r="D60" s="9"/>
-      <c r="E60" s="9"/>
-      <c r="F60" s="9"/>
-      <c r="G60" s="9"/>
-      <c r="H60" s="9"/>
+      <c r="A60" s="10"/>
+      <c r="B60" s="11"/>
+      <c r="C60" s="11"/>
+      <c r="D60" s="11"/>
+      <c r="E60" s="11"/>
+      <c r="F60" s="11"/>
+      <c r="G60" s="11"/>
+      <c r="H60" s="11"/>
       <c r="I60" s="4"/>
       <c r="J60" s="4"/>
       <c r="K60" s="4"/>
@@ -2279,14 +2329,14 @@
       <c r="Z60" s="4"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="8"/>
-      <c r="B61" s="9"/>
-      <c r="C61" s="9"/>
-      <c r="D61" s="9"/>
-      <c r="E61" s="9"/>
-      <c r="F61" s="9"/>
-      <c r="G61" s="9"/>
-      <c r="H61" s="9"/>
+      <c r="A61" s="10"/>
+      <c r="B61" s="11"/>
+      <c r="C61" s="11"/>
+      <c r="D61" s="11"/>
+      <c r="E61" s="11"/>
+      <c r="F61" s="11"/>
+      <c r="G61" s="11"/>
+      <c r="H61" s="11"/>
       <c r="I61" s="4"/>
       <c r="J61" s="4"/>
       <c r="K61" s="4"/>
@@ -2307,14 +2357,14 @@
       <c r="Z61" s="4"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="8"/>
-      <c r="B62" s="9"/>
-      <c r="C62" s="9"/>
-      <c r="D62" s="9"/>
-      <c r="E62" s="9"/>
-      <c r="F62" s="9"/>
-      <c r="G62" s="9"/>
-      <c r="H62" s="9"/>
+      <c r="A62" s="10"/>
+      <c r="B62" s="11"/>
+      <c r="C62" s="11"/>
+      <c r="D62" s="11"/>
+      <c r="E62" s="11"/>
+      <c r="F62" s="11"/>
+      <c r="G62" s="11"/>
+      <c r="H62" s="11"/>
       <c r="I62" s="4"/>
       <c r="J62" s="4"/>
       <c r="K62" s="4"/>
@@ -2335,14 +2385,14 @@
       <c r="Z62" s="4"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="8"/>
-      <c r="B63" s="9"/>
-      <c r="C63" s="9"/>
-      <c r="D63" s="9"/>
-      <c r="E63" s="9"/>
-      <c r="F63" s="9"/>
-      <c r="G63" s="9"/>
-      <c r="H63" s="9"/>
+      <c r="A63" s="10"/>
+      <c r="B63" s="11"/>
+      <c r="C63" s="11"/>
+      <c r="D63" s="11"/>
+      <c r="E63" s="11"/>
+      <c r="F63" s="11"/>
+      <c r="G63" s="11"/>
+      <c r="H63" s="11"/>
       <c r="I63" s="4"/>
       <c r="J63" s="4"/>
       <c r="K63" s="4"/>
@@ -2363,14 +2413,14 @@
       <c r="Z63" s="4"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="8"/>
-      <c r="B64" s="9"/>
-      <c r="C64" s="9"/>
-      <c r="D64" s="9"/>
-      <c r="E64" s="9"/>
-      <c r="F64" s="9"/>
-      <c r="G64" s="9"/>
-      <c r="H64" s="9"/>
+      <c r="A64" s="10"/>
+      <c r="B64" s="11"/>
+      <c r="C64" s="11"/>
+      <c r="D64" s="11"/>
+      <c r="E64" s="11"/>
+      <c r="F64" s="11"/>
+      <c r="G64" s="11"/>
+      <c r="H64" s="11"/>
       <c r="I64" s="4"/>
       <c r="J64" s="4"/>
       <c r="K64" s="4"/>
@@ -2391,14 +2441,14 @@
       <c r="Z64" s="4"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="8"/>
-      <c r="B65" s="9"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="9"/>
-      <c r="E65" s="9"/>
-      <c r="F65" s="9"/>
-      <c r="G65" s="9"/>
-      <c r="H65" s="9"/>
+      <c r="A65" s="10"/>
+      <c r="B65" s="11"/>
+      <c r="C65" s="11"/>
+      <c r="D65" s="11"/>
+      <c r="E65" s="11"/>
+      <c r="F65" s="11"/>
+      <c r="G65" s="11"/>
+      <c r="H65" s="11"/>
       <c r="I65" s="4"/>
       <c r="J65" s="4"/>
       <c r="K65" s="4"/>
@@ -2419,14 +2469,14 @@
       <c r="Z65" s="4"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="8"/>
-      <c r="B66" s="9"/>
-      <c r="C66" s="9"/>
-      <c r="D66" s="9"/>
-      <c r="E66" s="9"/>
-      <c r="F66" s="9"/>
-      <c r="G66" s="9"/>
-      <c r="H66" s="9"/>
+      <c r="A66" s="10"/>
+      <c r="B66" s="11"/>
+      <c r="C66" s="11"/>
+      <c r="D66" s="11"/>
+      <c r="E66" s="11"/>
+      <c r="F66" s="11"/>
+      <c r="G66" s="11"/>
+      <c r="H66" s="11"/>
       <c r="I66" s="4"/>
       <c r="J66" s="4"/>
       <c r="K66" s="4"/>
@@ -2447,14 +2497,14 @@
       <c r="Z66" s="4"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="8"/>
-      <c r="B67" s="9"/>
-      <c r="C67" s="9"/>
-      <c r="D67" s="9"/>
-      <c r="E67" s="9"/>
-      <c r="F67" s="9"/>
-      <c r="G67" s="9"/>
-      <c r="H67" s="9"/>
+      <c r="A67" s="10"/>
+      <c r="B67" s="11"/>
+      <c r="C67" s="11"/>
+      <c r="D67" s="11"/>
+      <c r="E67" s="11"/>
+      <c r="F67" s="11"/>
+      <c r="G67" s="11"/>
+      <c r="H67" s="11"/>
       <c r="I67" s="4"/>
       <c r="J67" s="4"/>
       <c r="K67" s="4"/>
@@ -2475,14 +2525,14 @@
       <c r="Z67" s="4"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="8"/>
-      <c r="B68" s="9"/>
-      <c r="C68" s="9"/>
-      <c r="D68" s="9"/>
-      <c r="E68" s="9"/>
-      <c r="F68" s="9"/>
-      <c r="G68" s="9"/>
-      <c r="H68" s="9"/>
+      <c r="A68" s="10"/>
+      <c r="B68" s="11"/>
+      <c r="C68" s="11"/>
+      <c r="D68" s="11"/>
+      <c r="E68" s="11"/>
+      <c r="F68" s="11"/>
+      <c r="G68" s="11"/>
+      <c r="H68" s="11"/>
       <c r="I68" s="4"/>
       <c r="J68" s="4"/>
       <c r="K68" s="4"/>
@@ -2503,14 +2553,14 @@
       <c r="Z68" s="4"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="8"/>
-      <c r="B69" s="9"/>
-      <c r="C69" s="9"/>
-      <c r="D69" s="9"/>
-      <c r="E69" s="9"/>
-      <c r="F69" s="9"/>
-      <c r="G69" s="9"/>
-      <c r="H69" s="9"/>
+      <c r="A69" s="10"/>
+      <c r="B69" s="11"/>
+      <c r="C69" s="11"/>
+      <c r="D69" s="11"/>
+      <c r="E69" s="11"/>
+      <c r="F69" s="11"/>
+      <c r="G69" s="11"/>
+      <c r="H69" s="11"/>
       <c r="I69" s="4"/>
       <c r="J69" s="4"/>
       <c r="K69" s="4"/>
@@ -2531,14 +2581,14 @@
       <c r="Z69" s="4"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="8"/>
-      <c r="B70" s="9"/>
-      <c r="C70" s="9"/>
-      <c r="D70" s="9"/>
-      <c r="E70" s="9"/>
-      <c r="F70" s="9"/>
-      <c r="G70" s="9"/>
-      <c r="H70" s="9"/>
+      <c r="A70" s="10"/>
+      <c r="B70" s="11"/>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="11"/>
+      <c r="F70" s="11"/>
+      <c r="G70" s="11"/>
+      <c r="H70" s="11"/>
       <c r="I70" s="4"/>
       <c r="J70" s="4"/>
       <c r="K70" s="4"/>
@@ -2559,14 +2609,14 @@
       <c r="Z70" s="4"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="8"/>
-      <c r="B71" s="9"/>
-      <c r="C71" s="9"/>
-      <c r="D71" s="9"/>
-      <c r="E71" s="9"/>
-      <c r="F71" s="9"/>
-      <c r="G71" s="9"/>
-      <c r="H71" s="9"/>
+      <c r="A71" s="10"/>
+      <c r="B71" s="11"/>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="11"/>
+      <c r="F71" s="11"/>
+      <c r="G71" s="11"/>
+      <c r="H71" s="11"/>
       <c r="I71" s="4"/>
       <c r="J71" s="4"/>
       <c r="K71" s="4"/>
@@ -2587,14 +2637,14 @@
       <c r="Z71" s="4"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="8"/>
-      <c r="B72" s="9"/>
-      <c r="C72" s="9"/>
-      <c r="D72" s="9"/>
-      <c r="E72" s="9"/>
-      <c r="F72" s="9"/>
-      <c r="G72" s="9"/>
-      <c r="H72" s="9"/>
+      <c r="A72" s="10"/>
+      <c r="B72" s="11"/>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="11"/>
+      <c r="F72" s="11"/>
+      <c r="G72" s="11"/>
+      <c r="H72" s="11"/>
       <c r="I72" s="4"/>
       <c r="J72" s="4"/>
       <c r="K72" s="4"/>
@@ -2615,14 +2665,14 @@
       <c r="Z72" s="4"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="8"/>
-      <c r="B73" s="9"/>
-      <c r="C73" s="9"/>
-      <c r="D73" s="9"/>
-      <c r="E73" s="9"/>
-      <c r="F73" s="9"/>
-      <c r="G73" s="9"/>
-      <c r="H73" s="9"/>
+      <c r="A73" s="10"/>
+      <c r="B73" s="11"/>
+      <c r="C73" s="11"/>
+      <c r="D73" s="11"/>
+      <c r="E73" s="11"/>
+      <c r="F73" s="11"/>
+      <c r="G73" s="11"/>
+      <c r="H73" s="11"/>
       <c r="I73" s="4"/>
       <c r="J73" s="4"/>
       <c r="K73" s="4"/>
@@ -2643,14 +2693,14 @@
       <c r="Z73" s="4"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="8"/>
-      <c r="B74" s="9"/>
-      <c r="C74" s="9"/>
-      <c r="D74" s="9"/>
-      <c r="E74" s="9"/>
-      <c r="F74" s="9"/>
-      <c r="G74" s="9"/>
-      <c r="H74" s="9"/>
+      <c r="A74" s="10"/>
+      <c r="B74" s="11"/>
+      <c r="C74" s="11"/>
+      <c r="D74" s="11"/>
+      <c r="E74" s="11"/>
+      <c r="F74" s="11"/>
+      <c r="G74" s="11"/>
+      <c r="H74" s="11"/>
       <c r="I74" s="4"/>
       <c r="J74" s="4"/>
       <c r="K74" s="4"/>
@@ -2671,14 +2721,14 @@
       <c r="Z74" s="4"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="8"/>
-      <c r="B75" s="9"/>
-      <c r="C75" s="9"/>
-      <c r="D75" s="9"/>
-      <c r="E75" s="9"/>
-      <c r="F75" s="9"/>
-      <c r="G75" s="9"/>
-      <c r="H75" s="9"/>
+      <c r="A75" s="10"/>
+      <c r="B75" s="11"/>
+      <c r="C75" s="11"/>
+      <c r="D75" s="11"/>
+      <c r="E75" s="11"/>
+      <c r="F75" s="11"/>
+      <c r="G75" s="11"/>
+      <c r="H75" s="11"/>
       <c r="I75" s="4"/>
       <c r="J75" s="4"/>
       <c r="K75" s="4"/>
@@ -2699,14 +2749,14 @@
       <c r="Z75" s="4"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="8"/>
-      <c r="B76" s="9"/>
-      <c r="C76" s="9"/>
-      <c r="D76" s="9"/>
-      <c r="E76" s="9"/>
-      <c r="F76" s="9"/>
-      <c r="G76" s="9"/>
-      <c r="H76" s="9"/>
+      <c r="A76" s="10"/>
+      <c r="B76" s="11"/>
+      <c r="C76" s="11"/>
+      <c r="D76" s="11"/>
+      <c r="E76" s="11"/>
+      <c r="F76" s="11"/>
+      <c r="G76" s="11"/>
+      <c r="H76" s="11"/>
       <c r="I76" s="4"/>
       <c r="J76" s="4"/>
       <c r="K76" s="4"/>
@@ -2727,14 +2777,14 @@
       <c r="Z76" s="4"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="8"/>
-      <c r="B77" s="9"/>
-      <c r="C77" s="9"/>
-      <c r="D77" s="9"/>
-      <c r="E77" s="9"/>
-      <c r="F77" s="9"/>
-      <c r="G77" s="9"/>
-      <c r="H77" s="9"/>
+      <c r="A77" s="10"/>
+      <c r="B77" s="11"/>
+      <c r="C77" s="11"/>
+      <c r="D77" s="11"/>
+      <c r="E77" s="11"/>
+      <c r="F77" s="11"/>
+      <c r="G77" s="11"/>
+      <c r="H77" s="11"/>
       <c r="I77" s="4"/>
       <c r="J77" s="4"/>
       <c r="K77" s="4"/>
@@ -2755,14 +2805,14 @@
       <c r="Z77" s="4"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="8"/>
-      <c r="B78" s="9"/>
-      <c r="C78" s="9"/>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
-      <c r="F78" s="9"/>
-      <c r="G78" s="9"/>
-      <c r="H78" s="9"/>
+      <c r="A78" s="10"/>
+      <c r="B78" s="11"/>
+      <c r="C78" s="11"/>
+      <c r="D78" s="11"/>
+      <c r="E78" s="11"/>
+      <c r="F78" s="11"/>
+      <c r="G78" s="11"/>
+      <c r="H78" s="11"/>
       <c r="I78" s="4"/>
       <c r="J78" s="4"/>
       <c r="K78" s="4"/>
@@ -2783,14 +2833,14 @@
       <c r="Z78" s="4"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="8"/>
-      <c r="B79" s="9"/>
-      <c r="C79" s="9"/>
-      <c r="D79" s="9"/>
-      <c r="E79" s="9"/>
-      <c r="F79" s="9"/>
-      <c r="G79" s="9"/>
-      <c r="H79" s="9"/>
+      <c r="A79" s="10"/>
+      <c r="B79" s="11"/>
+      <c r="C79" s="11"/>
+      <c r="D79" s="11"/>
+      <c r="E79" s="11"/>
+      <c r="F79" s="11"/>
+      <c r="G79" s="11"/>
+      <c r="H79" s="11"/>
       <c r="I79" s="4"/>
       <c r="J79" s="4"/>
       <c r="K79" s="4"/>
@@ -2811,14 +2861,14 @@
       <c r="Z79" s="4"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="8"/>
-      <c r="B80" s="9"/>
-      <c r="C80" s="9"/>
-      <c r="D80" s="9"/>
-      <c r="E80" s="9"/>
-      <c r="F80" s="9"/>
-      <c r="G80" s="9"/>
-      <c r="H80" s="9"/>
+      <c r="A80" s="10"/>
+      <c r="B80" s="11"/>
+      <c r="C80" s="11"/>
+      <c r="D80" s="11"/>
+      <c r="E80" s="11"/>
+      <c r="F80" s="11"/>
+      <c r="G80" s="11"/>
+      <c r="H80" s="11"/>
       <c r="I80" s="4"/>
       <c r="J80" s="4"/>
       <c r="K80" s="4"/>
@@ -2839,14 +2889,14 @@
       <c r="Z80" s="4"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="8"/>
-      <c r="B81" s="9"/>
-      <c r="C81" s="9"/>
-      <c r="D81" s="9"/>
-      <c r="E81" s="9"/>
-      <c r="F81" s="9"/>
-      <c r="G81" s="9"/>
-      <c r="H81" s="9"/>
+      <c r="A81" s="10"/>
+      <c r="B81" s="11"/>
+      <c r="C81" s="11"/>
+      <c r="D81" s="11"/>
+      <c r="E81" s="11"/>
+      <c r="F81" s="11"/>
+      <c r="G81" s="11"/>
+      <c r="H81" s="11"/>
       <c r="I81" s="4"/>
       <c r="J81" s="4"/>
       <c r="K81" s="4"/>
@@ -2867,14 +2917,14 @@
       <c r="Z81" s="4"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="8"/>
-      <c r="B82" s="9"/>
-      <c r="C82" s="9"/>
-      <c r="D82" s="9"/>
-      <c r="E82" s="9"/>
-      <c r="F82" s="9"/>
-      <c r="G82" s="9"/>
-      <c r="H82" s="9"/>
+      <c r="A82" s="10"/>
+      <c r="B82" s="11"/>
+      <c r="C82" s="11"/>
+      <c r="D82" s="11"/>
+      <c r="E82" s="11"/>
+      <c r="F82" s="11"/>
+      <c r="G82" s="11"/>
+      <c r="H82" s="11"/>
       <c r="I82" s="4"/>
       <c r="J82" s="4"/>
       <c r="K82" s="4"/>
@@ -2895,14 +2945,14 @@
       <c r="Z82" s="4"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="8"/>
-      <c r="B83" s="9"/>
-      <c r="C83" s="9"/>
-      <c r="D83" s="9"/>
-      <c r="E83" s="9"/>
-      <c r="F83" s="9"/>
-      <c r="G83" s="9"/>
-      <c r="H83" s="9"/>
+      <c r="A83" s="10"/>
+      <c r="B83" s="11"/>
+      <c r="C83" s="11"/>
+      <c r="D83" s="11"/>
+      <c r="E83" s="11"/>
+      <c r="F83" s="11"/>
+      <c r="G83" s="11"/>
+      <c r="H83" s="11"/>
       <c r="I83" s="4"/>
       <c r="J83" s="4"/>
       <c r="K83" s="4"/>
@@ -2923,14 +2973,14 @@
       <c r="Z83" s="4"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="8"/>
-      <c r="B84" s="9"/>
-      <c r="C84" s="9"/>
-      <c r="D84" s="9"/>
-      <c r="E84" s="9"/>
-      <c r="F84" s="9"/>
-      <c r="G84" s="9"/>
-      <c r="H84" s="9"/>
+      <c r="A84" s="10"/>
+      <c r="B84" s="11"/>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="11"/>
+      <c r="F84" s="11"/>
+      <c r="G84" s="11"/>
+      <c r="H84" s="11"/>
       <c r="I84" s="4"/>
       <c r="J84" s="4"/>
       <c r="K84" s="4"/>
@@ -2951,14 +3001,14 @@
       <c r="Z84" s="4"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="8"/>
-      <c r="B85" s="9"/>
-      <c r="C85" s="9"/>
-      <c r="D85" s="9"/>
-      <c r="E85" s="9"/>
-      <c r="F85" s="9"/>
-      <c r="G85" s="9"/>
-      <c r="H85" s="9"/>
+      <c r="A85" s="10"/>
+      <c r="B85" s="11"/>
+      <c r="C85" s="11"/>
+      <c r="D85" s="11"/>
+      <c r="E85" s="11"/>
+      <c r="F85" s="11"/>
+      <c r="G85" s="11"/>
+      <c r="H85" s="11"/>
       <c r="I85" s="4"/>
       <c r="J85" s="4"/>
       <c r="K85" s="4"/>
@@ -2979,14 +3029,14 @@
       <c r="Z85" s="4"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="8"/>
-      <c r="B86" s="9"/>
-      <c r="C86" s="9"/>
-      <c r="D86" s="9"/>
-      <c r="E86" s="9"/>
-      <c r="F86" s="9"/>
-      <c r="G86" s="9"/>
-      <c r="H86" s="9"/>
+      <c r="A86" s="10"/>
+      <c r="B86" s="11"/>
+      <c r="C86" s="11"/>
+      <c r="D86" s="11"/>
+      <c r="E86" s="11"/>
+      <c r="F86" s="11"/>
+      <c r="G86" s="11"/>
+      <c r="H86" s="11"/>
       <c r="I86" s="4"/>
       <c r="J86" s="4"/>
       <c r="K86" s="4"/>
@@ -3007,14 +3057,14 @@
       <c r="Z86" s="4"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="8"/>
-      <c r="B87" s="9"/>
-      <c r="C87" s="9"/>
-      <c r="D87" s="9"/>
-      <c r="E87" s="9"/>
-      <c r="F87" s="9"/>
-      <c r="G87" s="9"/>
-      <c r="H87" s="9"/>
+      <c r="A87" s="10"/>
+      <c r="B87" s="11"/>
+      <c r="C87" s="11"/>
+      <c r="D87" s="11"/>
+      <c r="E87" s="11"/>
+      <c r="F87" s="11"/>
+      <c r="G87" s="11"/>
+      <c r="H87" s="11"/>
       <c r="I87" s="4"/>
       <c r="J87" s="4"/>
       <c r="K87" s="4"/>
@@ -3035,14 +3085,14 @@
       <c r="Z87" s="4"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="8"/>
-      <c r="B88" s="9"/>
-      <c r="C88" s="9"/>
-      <c r="D88" s="9"/>
-      <c r="E88" s="9"/>
-      <c r="F88" s="9"/>
-      <c r="G88" s="9"/>
-      <c r="H88" s="9"/>
+      <c r="A88" s="10"/>
+      <c r="B88" s="11"/>
+      <c r="C88" s="11"/>
+      <c r="D88" s="11"/>
+      <c r="E88" s="11"/>
+      <c r="F88" s="11"/>
+      <c r="G88" s="11"/>
+      <c r="H88" s="11"/>
       <c r="I88" s="4"/>
       <c r="J88" s="4"/>
       <c r="K88" s="4"/>
@@ -3063,14 +3113,14 @@
       <c r="Z88" s="4"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="8"/>
-      <c r="B89" s="9"/>
-      <c r="C89" s="9"/>
-      <c r="D89" s="9"/>
-      <c r="E89" s="9"/>
-      <c r="F89" s="9"/>
-      <c r="G89" s="9"/>
-      <c r="H89" s="9"/>
+      <c r="A89" s="10"/>
+      <c r="B89" s="11"/>
+      <c r="C89" s="11"/>
+      <c r="D89" s="11"/>
+      <c r="E89" s="11"/>
+      <c r="F89" s="11"/>
+      <c r="G89" s="11"/>
+      <c r="H89" s="11"/>
       <c r="I89" s="4"/>
       <c r="J89" s="4"/>
       <c r="K89" s="4"/>
@@ -3091,14 +3141,14 @@
       <c r="Z89" s="4"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="8"/>
-      <c r="B90" s="9"/>
-      <c r="C90" s="9"/>
-      <c r="D90" s="9"/>
-      <c r="E90" s="9"/>
-      <c r="F90" s="9"/>
-      <c r="G90" s="9"/>
-      <c r="H90" s="9"/>
+      <c r="A90" s="10"/>
+      <c r="B90" s="11"/>
+      <c r="C90" s="11"/>
+      <c r="D90" s="11"/>
+      <c r="E90" s="11"/>
+      <c r="F90" s="11"/>
+      <c r="G90" s="11"/>
+      <c r="H90" s="11"/>
       <c r="I90" s="4"/>
       <c r="J90" s="4"/>
       <c r="K90" s="4"/>
@@ -3119,14 +3169,14 @@
       <c r="Z90" s="4"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="8"/>
-      <c r="B91" s="9"/>
-      <c r="C91" s="9"/>
-      <c r="D91" s="9"/>
-      <c r="E91" s="9"/>
-      <c r="F91" s="9"/>
-      <c r="G91" s="9"/>
-      <c r="H91" s="9"/>
+      <c r="A91" s="10"/>
+      <c r="B91" s="11"/>
+      <c r="C91" s="11"/>
+      <c r="D91" s="11"/>
+      <c r="E91" s="11"/>
+      <c r="F91" s="11"/>
+      <c r="G91" s="11"/>
+      <c r="H91" s="11"/>
       <c r="I91" s="4"/>
       <c r="J91" s="4"/>
       <c r="K91" s="4"/>
@@ -3147,14 +3197,14 @@
       <c r="Z91" s="4"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="8"/>
-      <c r="B92" s="9"/>
-      <c r="C92" s="9"/>
-      <c r="D92" s="9"/>
-      <c r="E92" s="9"/>
-      <c r="F92" s="9"/>
-      <c r="G92" s="9"/>
-      <c r="H92" s="9"/>
+      <c r="A92" s="10"/>
+      <c r="B92" s="11"/>
+      <c r="C92" s="11"/>
+      <c r="D92" s="11"/>
+      <c r="E92" s="11"/>
+      <c r="F92" s="11"/>
+      <c r="G92" s="11"/>
+      <c r="H92" s="11"/>
       <c r="I92" s="4"/>
       <c r="J92" s="4"/>
       <c r="K92" s="4"/>
@@ -3175,14 +3225,14 @@
       <c r="Z92" s="4"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="8"/>
-      <c r="B93" s="9"/>
-      <c r="C93" s="9"/>
-      <c r="D93" s="9"/>
-      <c r="E93" s="9"/>
-      <c r="F93" s="9"/>
-      <c r="G93" s="9"/>
-      <c r="H93" s="9"/>
+      <c r="A93" s="10"/>
+      <c r="B93" s="11"/>
+      <c r="C93" s="11"/>
+      <c r="D93" s="11"/>
+      <c r="E93" s="11"/>
+      <c r="F93" s="11"/>
+      <c r="G93" s="11"/>
+      <c r="H93" s="11"/>
       <c r="I93" s="4"/>
       <c r="J93" s="4"/>
       <c r="K93" s="4"/>
@@ -3203,14 +3253,14 @@
       <c r="Z93" s="4"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="8"/>
-      <c r="B94" s="9"/>
-      <c r="C94" s="9"/>
-      <c r="D94" s="9"/>
-      <c r="E94" s="9"/>
-      <c r="F94" s="9"/>
-      <c r="G94" s="9"/>
-      <c r="H94" s="9"/>
+      <c r="A94" s="10"/>
+      <c r="B94" s="11"/>
+      <c r="C94" s="11"/>
+      <c r="D94" s="11"/>
+      <c r="E94" s="11"/>
+      <c r="F94" s="11"/>
+      <c r="G94" s="11"/>
+      <c r="H94" s="11"/>
       <c r="I94" s="4"/>
       <c r="J94" s="4"/>
       <c r="K94" s="4"/>
@@ -3231,14 +3281,14 @@
       <c r="Z94" s="4"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="8"/>
-      <c r="B95" s="9"/>
-      <c r="C95" s="9"/>
-      <c r="D95" s="9"/>
-      <c r="E95" s="9"/>
-      <c r="F95" s="9"/>
-      <c r="G95" s="9"/>
-      <c r="H95" s="9"/>
+      <c r="A95" s="10"/>
+      <c r="B95" s="11"/>
+      <c r="C95" s="11"/>
+      <c r="D95" s="11"/>
+      <c r="E95" s="11"/>
+      <c r="F95" s="11"/>
+      <c r="G95" s="11"/>
+      <c r="H95" s="11"/>
       <c r="I95" s="4"/>
       <c r="J95" s="4"/>
       <c r="K95" s="4"/>
@@ -3259,14 +3309,14 @@
       <c r="Z95" s="4"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="8"/>
-      <c r="B96" s="9"/>
-      <c r="C96" s="9"/>
-      <c r="D96" s="9"/>
-      <c r="E96" s="9"/>
-      <c r="F96" s="9"/>
-      <c r="G96" s="9"/>
-      <c r="H96" s="9"/>
+      <c r="A96" s="10"/>
+      <c r="B96" s="11"/>
+      <c r="C96" s="11"/>
+      <c r="D96" s="11"/>
+      <c r="E96" s="11"/>
+      <c r="F96" s="11"/>
+      <c r="G96" s="11"/>
+      <c r="H96" s="11"/>
       <c r="I96" s="4"/>
       <c r="J96" s="4"/>
       <c r="K96" s="4"/>
@@ -3287,14 +3337,14 @@
       <c r="Z96" s="4"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="8"/>
-      <c r="B97" s="9"/>
-      <c r="C97" s="9"/>
-      <c r="D97" s="9"/>
-      <c r="E97" s="9"/>
-      <c r="F97" s="9"/>
-      <c r="G97" s="9"/>
-      <c r="H97" s="9"/>
+      <c r="A97" s="10"/>
+      <c r="B97" s="11"/>
+      <c r="C97" s="11"/>
+      <c r="D97" s="11"/>
+      <c r="E97" s="11"/>
+      <c r="F97" s="11"/>
+      <c r="G97" s="11"/>
+      <c r="H97" s="11"/>
       <c r="I97" s="4"/>
       <c r="J97" s="4"/>
       <c r="K97" s="4"/>
@@ -3315,14 +3365,14 @@
       <c r="Z97" s="4"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="8"/>
-      <c r="B98" s="9"/>
-      <c r="C98" s="9"/>
-      <c r="D98" s="9"/>
-      <c r="E98" s="9"/>
-      <c r="F98" s="9"/>
-      <c r="G98" s="9"/>
-      <c r="H98" s="9"/>
+      <c r="A98" s="10"/>
+      <c r="B98" s="11"/>
+      <c r="C98" s="11"/>
+      <c r="D98" s="11"/>
+      <c r="E98" s="11"/>
+      <c r="F98" s="11"/>
+      <c r="G98" s="11"/>
+      <c r="H98" s="11"/>
       <c r="I98" s="4"/>
       <c r="J98" s="4"/>
       <c r="K98" s="4"/>
@@ -3343,14 +3393,14 @@
       <c r="Z98" s="4"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="8"/>
-      <c r="B99" s="9"/>
-      <c r="C99" s="9"/>
-      <c r="D99" s="9"/>
-      <c r="E99" s="9"/>
-      <c r="F99" s="9"/>
-      <c r="G99" s="9"/>
-      <c r="H99" s="9"/>
+      <c r="A99" s="10"/>
+      <c r="B99" s="11"/>
+      <c r="C99" s="11"/>
+      <c r="D99" s="11"/>
+      <c r="E99" s="11"/>
+      <c r="F99" s="11"/>
+      <c r="G99" s="11"/>
+      <c r="H99" s="11"/>
       <c r="I99" s="4"/>
       <c r="J99" s="4"/>
       <c r="K99" s="4"/>
@@ -3371,14 +3421,14 @@
       <c r="Z99" s="4"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="8"/>
-      <c r="B100" s="9"/>
-      <c r="C100" s="9"/>
-      <c r="D100" s="9"/>
-      <c r="E100" s="9"/>
-      <c r="F100" s="9"/>
-      <c r="G100" s="9"/>
-      <c r="H100" s="9"/>
+      <c r="A100" s="10"/>
+      <c r="B100" s="11"/>
+      <c r="C100" s="11"/>
+      <c r="D100" s="11"/>
+      <c r="E100" s="11"/>
+      <c r="F100" s="11"/>
+      <c r="G100" s="11"/>
+      <c r="H100" s="11"/>
       <c r="I100" s="4"/>
       <c r="J100" s="4"/>
       <c r="K100" s="4"/>
@@ -3399,14 +3449,14 @@
       <c r="Z100" s="4"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="8"/>
-      <c r="B101" s="9"/>
-      <c r="C101" s="9"/>
-      <c r="D101" s="9"/>
-      <c r="E101" s="9"/>
-      <c r="F101" s="9"/>
-      <c r="G101" s="9"/>
-      <c r="H101" s="9"/>
+      <c r="A101" s="10"/>
+      <c r="B101" s="11"/>
+      <c r="C101" s="11"/>
+      <c r="D101" s="11"/>
+      <c r="E101" s="11"/>
+      <c r="F101" s="11"/>
+      <c r="G101" s="11"/>
+      <c r="H101" s="11"/>
       <c r="I101" s="4"/>
       <c r="J101" s="4"/>
       <c r="K101" s="4"/>
@@ -3427,14 +3477,14 @@
       <c r="Z101" s="4"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="8"/>
-      <c r="B102" s="9"/>
-      <c r="C102" s="9"/>
-      <c r="D102" s="9"/>
-      <c r="E102" s="9"/>
-      <c r="F102" s="9"/>
-      <c r="G102" s="9"/>
-      <c r="H102" s="9"/>
+      <c r="A102" s="10"/>
+      <c r="B102" s="11"/>
+      <c r="C102" s="11"/>
+      <c r="D102" s="11"/>
+      <c r="E102" s="11"/>
+      <c r="F102" s="11"/>
+      <c r="G102" s="11"/>
+      <c r="H102" s="11"/>
       <c r="I102" s="4"/>
       <c r="J102" s="4"/>
       <c r="K102" s="4"/>
@@ -3455,14 +3505,14 @@
       <c r="Z102" s="4"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="8"/>
-      <c r="B103" s="9"/>
-      <c r="C103" s="9"/>
-      <c r="D103" s="9"/>
-      <c r="E103" s="9"/>
-      <c r="F103" s="9"/>
-      <c r="G103" s="9"/>
-      <c r="H103" s="9"/>
+      <c r="A103" s="10"/>
+      <c r="B103" s="11"/>
+      <c r="C103" s="11"/>
+      <c r="D103" s="11"/>
+      <c r="E103" s="11"/>
+      <c r="F103" s="11"/>
+      <c r="G103" s="11"/>
+      <c r="H103" s="11"/>
       <c r="I103" s="4"/>
       <c r="J103" s="4"/>
       <c r="K103" s="4"/>
@@ -3483,14 +3533,14 @@
       <c r="Z103" s="4"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="8"/>
-      <c r="B104" s="9"/>
-      <c r="C104" s="9"/>
-      <c r="D104" s="9"/>
-      <c r="E104" s="9"/>
-      <c r="F104" s="9"/>
-      <c r="G104" s="9"/>
-      <c r="H104" s="9"/>
+      <c r="A104" s="10"/>
+      <c r="B104" s="11"/>
+      <c r="C104" s="11"/>
+      <c r="D104" s="11"/>
+      <c r="E104" s="11"/>
+      <c r="F104" s="11"/>
+      <c r="G104" s="11"/>
+      <c r="H104" s="11"/>
       <c r="I104" s="4"/>
       <c r="J104" s="4"/>
       <c r="K104" s="4"/>
@@ -3511,14 +3561,14 @@
       <c r="Z104" s="4"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="8"/>
-      <c r="B105" s="9"/>
-      <c r="C105" s="9"/>
-      <c r="D105" s="9"/>
-      <c r="E105" s="9"/>
-      <c r="F105" s="9"/>
-      <c r="G105" s="9"/>
-      <c r="H105" s="9"/>
+      <c r="A105" s="10"/>
+      <c r="B105" s="11"/>
+      <c r="C105" s="11"/>
+      <c r="D105" s="11"/>
+      <c r="E105" s="11"/>
+      <c r="F105" s="11"/>
+      <c r="G105" s="11"/>
+      <c r="H105" s="11"/>
       <c r="I105" s="4"/>
       <c r="J105" s="4"/>
       <c r="K105" s="4"/>
@@ -3539,14 +3589,14 @@
       <c r="Z105" s="4"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="8"/>
-      <c r="B106" s="9"/>
-      <c r="C106" s="9"/>
-      <c r="D106" s="9"/>
-      <c r="E106" s="9"/>
-      <c r="F106" s="9"/>
-      <c r="G106" s="9"/>
-      <c r="H106" s="9"/>
+      <c r="A106" s="10"/>
+      <c r="B106" s="11"/>
+      <c r="C106" s="11"/>
+      <c r="D106" s="11"/>
+      <c r="E106" s="11"/>
+      <c r="F106" s="11"/>
+      <c r="G106" s="11"/>
+      <c r="H106" s="11"/>
       <c r="I106" s="4"/>
       <c r="J106" s="4"/>
       <c r="K106" s="4"/>
@@ -3567,14 +3617,14 @@
       <c r="Z106" s="4"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="8"/>
-      <c r="B107" s="9"/>
-      <c r="C107" s="9"/>
-      <c r="D107" s="9"/>
-      <c r="E107" s="9"/>
-      <c r="F107" s="9"/>
-      <c r="G107" s="9"/>
-      <c r="H107" s="9"/>
+      <c r="A107" s="10"/>
+      <c r="B107" s="11"/>
+      <c r="C107" s="11"/>
+      <c r="D107" s="11"/>
+      <c r="E107" s="11"/>
+      <c r="F107" s="11"/>
+      <c r="G107" s="11"/>
+      <c r="H107" s="11"/>
       <c r="I107" s="4"/>
       <c r="J107" s="4"/>
       <c r="K107" s="4"/>
@@ -3595,14 +3645,14 @@
       <c r="Z107" s="4"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="8"/>
-      <c r="B108" s="9"/>
-      <c r="C108" s="9"/>
-      <c r="D108" s="9"/>
-      <c r="E108" s="9"/>
-      <c r="F108" s="9"/>
-      <c r="G108" s="9"/>
-      <c r="H108" s="9"/>
+      <c r="A108" s="10"/>
+      <c r="B108" s="11"/>
+      <c r="C108" s="11"/>
+      <c r="D108" s="11"/>
+      <c r="E108" s="11"/>
+      <c r="F108" s="11"/>
+      <c r="G108" s="11"/>
+      <c r="H108" s="11"/>
       <c r="I108" s="4"/>
       <c r="J108" s="4"/>
       <c r="K108" s="4"/>
@@ -3623,14 +3673,14 @@
       <c r="Z108" s="4"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="8"/>
-      <c r="B109" s="9"/>
-      <c r="C109" s="9"/>
-      <c r="D109" s="9"/>
-      <c r="E109" s="9"/>
-      <c r="F109" s="9"/>
-      <c r="G109" s="9"/>
-      <c r="H109" s="9"/>
+      <c r="A109" s="10"/>
+      <c r="B109" s="11"/>
+      <c r="C109" s="11"/>
+      <c r="D109" s="11"/>
+      <c r="E109" s="11"/>
+      <c r="F109" s="11"/>
+      <c r="G109" s="11"/>
+      <c r="H109" s="11"/>
       <c r="I109" s="4"/>
       <c r="J109" s="4"/>
       <c r="K109" s="4"/>
@@ -3651,14 +3701,14 @@
       <c r="Z109" s="4"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="8"/>
-      <c r="B110" s="9"/>
-      <c r="C110" s="9"/>
-      <c r="D110" s="9"/>
-      <c r="E110" s="9"/>
-      <c r="F110" s="9"/>
-      <c r="G110" s="9"/>
-      <c r="H110" s="9"/>
+      <c r="A110" s="10"/>
+      <c r="B110" s="11"/>
+      <c r="C110" s="11"/>
+      <c r="D110" s="11"/>
+      <c r="E110" s="11"/>
+      <c r="F110" s="11"/>
+      <c r="G110" s="11"/>
+      <c r="H110" s="11"/>
       <c r="I110" s="4"/>
       <c r="J110" s="4"/>
       <c r="K110" s="4"/>
@@ -3679,14 +3729,14 @@
       <c r="Z110" s="4"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="8"/>
-      <c r="B111" s="9"/>
-      <c r="C111" s="9"/>
-      <c r="D111" s="9"/>
-      <c r="E111" s="9"/>
-      <c r="F111" s="9"/>
-      <c r="G111" s="9"/>
-      <c r="H111" s="9"/>
+      <c r="A111" s="10"/>
+      <c r="B111" s="11"/>
+      <c r="C111" s="11"/>
+      <c r="D111" s="11"/>
+      <c r="E111" s="11"/>
+      <c r="F111" s="11"/>
+      <c r="G111" s="11"/>
+      <c r="H111" s="11"/>
       <c r="I111" s="4"/>
       <c r="J111" s="4"/>
       <c r="K111" s="4"/>
@@ -3707,14 +3757,14 @@
       <c r="Z111" s="4"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="8"/>
-      <c r="B112" s="9"/>
-      <c r="C112" s="9"/>
-      <c r="D112" s="9"/>
-      <c r="E112" s="9"/>
-      <c r="F112" s="9"/>
-      <c r="G112" s="9"/>
-      <c r="H112" s="9"/>
+      <c r="A112" s="10"/>
+      <c r="B112" s="11"/>
+      <c r="C112" s="11"/>
+      <c r="D112" s="11"/>
+      <c r="E112" s="11"/>
+      <c r="F112" s="11"/>
+      <c r="G112" s="11"/>
+      <c r="H112" s="11"/>
       <c r="I112" s="4"/>
       <c r="J112" s="4"/>
       <c r="K112" s="4"/>
@@ -3735,14 +3785,14 @@
       <c r="Z112" s="4"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="8"/>
-      <c r="B113" s="9"/>
-      <c r="C113" s="9"/>
-      <c r="D113" s="9"/>
-      <c r="E113" s="9"/>
-      <c r="F113" s="9"/>
-      <c r="G113" s="9"/>
-      <c r="H113" s="9"/>
+      <c r="A113" s="10"/>
+      <c r="B113" s="11"/>
+      <c r="C113" s="11"/>
+      <c r="D113" s="11"/>
+      <c r="E113" s="11"/>
+      <c r="F113" s="11"/>
+      <c r="G113" s="11"/>
+      <c r="H113" s="11"/>
       <c r="I113" s="4"/>
       <c r="J113" s="4"/>
       <c r="K113" s="4"/>
@@ -3763,14 +3813,14 @@
       <c r="Z113" s="4"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="8"/>
-      <c r="B114" s="9"/>
-      <c r="C114" s="9"/>
-      <c r="D114" s="9"/>
-      <c r="E114" s="9"/>
-      <c r="F114" s="9"/>
-      <c r="G114" s="9"/>
-      <c r="H114" s="9"/>
+      <c r="A114" s="10"/>
+      <c r="B114" s="11"/>
+      <c r="C114" s="11"/>
+      <c r="D114" s="11"/>
+      <c r="E114" s="11"/>
+      <c r="F114" s="11"/>
+      <c r="G114" s="11"/>
+      <c r="H114" s="11"/>
       <c r="I114" s="4"/>
       <c r="J114" s="4"/>
       <c r="K114" s="4"/>
@@ -3791,14 +3841,14 @@
       <c r="Z114" s="4"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="8"/>
-      <c r="B115" s="9"/>
-      <c r="C115" s="9"/>
-      <c r="D115" s="9"/>
-      <c r="E115" s="9"/>
-      <c r="F115" s="9"/>
-      <c r="G115" s="9"/>
-      <c r="H115" s="9"/>
+      <c r="A115" s="10"/>
+      <c r="B115" s="11"/>
+      <c r="C115" s="11"/>
+      <c r="D115" s="11"/>
+      <c r="E115" s="11"/>
+      <c r="F115" s="11"/>
+      <c r="G115" s="11"/>
+      <c r="H115" s="11"/>
       <c r="I115" s="4"/>
       <c r="J115" s="4"/>
       <c r="K115" s="4"/>
@@ -3819,14 +3869,14 @@
       <c r="Z115" s="4"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="8"/>
-      <c r="B116" s="9"/>
-      <c r="C116" s="9"/>
-      <c r="D116" s="9"/>
-      <c r="E116" s="9"/>
-      <c r="F116" s="9"/>
-      <c r="G116" s="9"/>
-      <c r="H116" s="9"/>
+      <c r="A116" s="10"/>
+      <c r="B116" s="11"/>
+      <c r="C116" s="11"/>
+      <c r="D116" s="11"/>
+      <c r="E116" s="11"/>
+      <c r="F116" s="11"/>
+      <c r="G116" s="11"/>
+      <c r="H116" s="11"/>
       <c r="I116" s="4"/>
       <c r="J116" s="4"/>
       <c r="K116" s="4"/>
@@ -3847,14 +3897,14 @@
       <c r="Z116" s="4"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="8"/>
-      <c r="B117" s="9"/>
-      <c r="C117" s="9"/>
-      <c r="D117" s="9"/>
-      <c r="E117" s="9"/>
-      <c r="F117" s="9"/>
-      <c r="G117" s="9"/>
-      <c r="H117" s="9"/>
+      <c r="A117" s="10"/>
+      <c r="B117" s="11"/>
+      <c r="C117" s="11"/>
+      <c r="D117" s="11"/>
+      <c r="E117" s="11"/>
+      <c r="F117" s="11"/>
+      <c r="G117" s="11"/>
+      <c r="H117" s="11"/>
       <c r="I117" s="4"/>
       <c r="J117" s="4"/>
       <c r="K117" s="4"/>
@@ -3875,14 +3925,14 @@
       <c r="Z117" s="4"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="8"/>
-      <c r="B118" s="9"/>
-      <c r="C118" s="9"/>
-      <c r="D118" s="9"/>
-      <c r="E118" s="9"/>
-      <c r="F118" s="9"/>
-      <c r="G118" s="9"/>
-      <c r="H118" s="9"/>
+      <c r="A118" s="10"/>
+      <c r="B118" s="11"/>
+      <c r="C118" s="11"/>
+      <c r="D118" s="11"/>
+      <c r="E118" s="11"/>
+      <c r="F118" s="11"/>
+      <c r="G118" s="11"/>
+      <c r="H118" s="11"/>
       <c r="I118" s="4"/>
       <c r="J118" s="4"/>
       <c r="K118" s="4"/>
@@ -3903,14 +3953,14 @@
       <c r="Z118" s="4"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="8"/>
-      <c r="B119" s="9"/>
-      <c r="C119" s="9"/>
-      <c r="D119" s="9"/>
-      <c r="E119" s="9"/>
-      <c r="F119" s="9"/>
-      <c r="G119" s="9"/>
-      <c r="H119" s="9"/>
+      <c r="A119" s="10"/>
+      <c r="B119" s="11"/>
+      <c r="C119" s="11"/>
+      <c r="D119" s="11"/>
+      <c r="E119" s="11"/>
+      <c r="F119" s="11"/>
+      <c r="G119" s="11"/>
+      <c r="H119" s="11"/>
       <c r="I119" s="4"/>
       <c r="J119" s="4"/>
       <c r="K119" s="4"/>
@@ -3931,14 +3981,14 @@
       <c r="Z119" s="4"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="8"/>
-      <c r="B120" s="9"/>
-      <c r="C120" s="9"/>
-      <c r="D120" s="9"/>
-      <c r="E120" s="9"/>
-      <c r="F120" s="9"/>
-      <c r="G120" s="9"/>
-      <c r="H120" s="9"/>
+      <c r="A120" s="10"/>
+      <c r="B120" s="11"/>
+      <c r="C120" s="11"/>
+      <c r="D120" s="11"/>
+      <c r="E120" s="11"/>
+      <c r="F120" s="11"/>
+      <c r="G120" s="11"/>
+      <c r="H120" s="11"/>
       <c r="I120" s="4"/>
       <c r="J120" s="4"/>
       <c r="K120" s="4"/>
@@ -3959,14 +4009,14 @@
       <c r="Z120" s="4"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="8"/>
-      <c r="B121" s="9"/>
-      <c r="C121" s="9"/>
-      <c r="D121" s="9"/>
-      <c r="E121" s="9"/>
-      <c r="F121" s="9"/>
-      <c r="G121" s="9"/>
-      <c r="H121" s="9"/>
+      <c r="A121" s="10"/>
+      <c r="B121" s="11"/>
+      <c r="C121" s="11"/>
+      <c r="D121" s="11"/>
+      <c r="E121" s="11"/>
+      <c r="F121" s="11"/>
+      <c r="G121" s="11"/>
+      <c r="H121" s="11"/>
       <c r="I121" s="4"/>
       <c r="J121" s="4"/>
       <c r="K121" s="4"/>
@@ -3987,14 +4037,14 @@
       <c r="Z121" s="4"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="8"/>
-      <c r="B122" s="9"/>
-      <c r="C122" s="9"/>
-      <c r="D122" s="9"/>
-      <c r="E122" s="9"/>
-      <c r="F122" s="9"/>
-      <c r="G122" s="9"/>
-      <c r="H122" s="9"/>
+      <c r="A122" s="10"/>
+      <c r="B122" s="11"/>
+      <c r="C122" s="11"/>
+      <c r="D122" s="11"/>
+      <c r="E122" s="11"/>
+      <c r="F122" s="11"/>
+      <c r="G122" s="11"/>
+      <c r="H122" s="11"/>
       <c r="I122" s="4"/>
       <c r="J122" s="4"/>
       <c r="K122" s="4"/>
@@ -4015,14 +4065,14 @@
       <c r="Z122" s="4"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="8"/>
-      <c r="B123" s="9"/>
-      <c r="C123" s="9"/>
-      <c r="D123" s="9"/>
-      <c r="E123" s="9"/>
-      <c r="F123" s="9"/>
-      <c r="G123" s="9"/>
-      <c r="H123" s="9"/>
+      <c r="A123" s="10"/>
+      <c r="B123" s="11"/>
+      <c r="C123" s="11"/>
+      <c r="D123" s="11"/>
+      <c r="E123" s="11"/>
+      <c r="F123" s="11"/>
+      <c r="G123" s="11"/>
+      <c r="H123" s="11"/>
       <c r="I123" s="4"/>
       <c r="J123" s="4"/>
       <c r="K123" s="4"/>
@@ -4043,14 +4093,14 @@
       <c r="Z123" s="4"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="8"/>
-      <c r="B124" s="9"/>
-      <c r="C124" s="9"/>
-      <c r="D124" s="9"/>
-      <c r="E124" s="9"/>
-      <c r="F124" s="9"/>
-      <c r="G124" s="9"/>
-      <c r="H124" s="9"/>
+      <c r="A124" s="10"/>
+      <c r="B124" s="11"/>
+      <c r="C124" s="11"/>
+      <c r="D124" s="11"/>
+      <c r="E124" s="11"/>
+      <c r="F124" s="11"/>
+      <c r="G124" s="11"/>
+      <c r="H124" s="11"/>
       <c r="I124" s="4"/>
       <c r="J124" s="4"/>
       <c r="K124" s="4"/>
@@ -4071,14 +4121,14 @@
       <c r="Z124" s="4"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="A125" s="8"/>
-      <c r="B125" s="9"/>
-      <c r="C125" s="9"/>
-      <c r="D125" s="9"/>
-      <c r="E125" s="9"/>
-      <c r="F125" s="9"/>
-      <c r="G125" s="9"/>
-      <c r="H125" s="9"/>
+      <c r="A125" s="10"/>
+      <c r="B125" s="11"/>
+      <c r="C125" s="11"/>
+      <c r="D125" s="11"/>
+      <c r="E125" s="11"/>
+      <c r="F125" s="11"/>
+      <c r="G125" s="11"/>
+      <c r="H125" s="11"/>
       <c r="I125" s="4"/>
       <c r="J125" s="4"/>
       <c r="K125" s="4"/>
@@ -4099,14 +4149,14 @@
       <c r="Z125" s="4"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="8"/>
-      <c r="B126" s="9"/>
-      <c r="C126" s="9"/>
-      <c r="D126" s="9"/>
-      <c r="E126" s="9"/>
-      <c r="F126" s="9"/>
-      <c r="G126" s="9"/>
-      <c r="H126" s="9"/>
+      <c r="A126" s="10"/>
+      <c r="B126" s="11"/>
+      <c r="C126" s="11"/>
+      <c r="D126" s="11"/>
+      <c r="E126" s="11"/>
+      <c r="F126" s="11"/>
+      <c r="G126" s="11"/>
+      <c r="H126" s="11"/>
       <c r="I126" s="4"/>
       <c r="J126" s="4"/>
       <c r="K126" s="4"/>
@@ -4127,14 +4177,14 @@
       <c r="Z126" s="4"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="8"/>
-      <c r="B127" s="9"/>
-      <c r="C127" s="9"/>
-      <c r="D127" s="9"/>
-      <c r="E127" s="9"/>
-      <c r="F127" s="9"/>
-      <c r="G127" s="9"/>
-      <c r="H127" s="9"/>
+      <c r="A127" s="10"/>
+      <c r="B127" s="11"/>
+      <c r="C127" s="11"/>
+      <c r="D127" s="11"/>
+      <c r="E127" s="11"/>
+      <c r="F127" s="11"/>
+      <c r="G127" s="11"/>
+      <c r="H127" s="11"/>
       <c r="I127" s="4"/>
       <c r="J127" s="4"/>
       <c r="K127" s="4"/>
@@ -4155,14 +4205,14 @@
       <c r="Z127" s="4"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="8"/>
-      <c r="B128" s="9"/>
-      <c r="C128" s="9"/>
-      <c r="D128" s="9"/>
-      <c r="E128" s="9"/>
-      <c r="F128" s="9"/>
-      <c r="G128" s="9"/>
-      <c r="H128" s="9"/>
+      <c r="A128" s="10"/>
+      <c r="B128" s="11"/>
+      <c r="C128" s="11"/>
+      <c r="D128" s="11"/>
+      <c r="E128" s="11"/>
+      <c r="F128" s="11"/>
+      <c r="G128" s="11"/>
+      <c r="H128" s="11"/>
       <c r="I128" s="4"/>
       <c r="J128" s="4"/>
       <c r="K128" s="4"/>
@@ -4183,14 +4233,14 @@
       <c r="Z128" s="4"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="8"/>
-      <c r="B129" s="9"/>
-      <c r="C129" s="9"/>
-      <c r="D129" s="9"/>
-      <c r="E129" s="9"/>
-      <c r="F129" s="9"/>
-      <c r="G129" s="9"/>
-      <c r="H129" s="9"/>
+      <c r="A129" s="10"/>
+      <c r="B129" s="11"/>
+      <c r="C129" s="11"/>
+      <c r="D129" s="11"/>
+      <c r="E129" s="11"/>
+      <c r="F129" s="11"/>
+      <c r="G129" s="11"/>
+      <c r="H129" s="11"/>
       <c r="I129" s="4"/>
       <c r="J129" s="4"/>
       <c r="K129" s="4"/>
@@ -4211,14 +4261,14 @@
       <c r="Z129" s="4"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="8"/>
-      <c r="B130" s="9"/>
-      <c r="C130" s="9"/>
-      <c r="D130" s="9"/>
-      <c r="E130" s="9"/>
-      <c r="F130" s="9"/>
-      <c r="G130" s="9"/>
-      <c r="H130" s="9"/>
+      <c r="A130" s="10"/>
+      <c r="B130" s="11"/>
+      <c r="C130" s="11"/>
+      <c r="D130" s="11"/>
+      <c r="E130" s="11"/>
+      <c r="F130" s="11"/>
+      <c r="G130" s="11"/>
+      <c r="H130" s="11"/>
       <c r="I130" s="4"/>
       <c r="J130" s="4"/>
       <c r="K130" s="4"/>
@@ -4239,14 +4289,14 @@
       <c r="Z130" s="4"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="8"/>
-      <c r="B131" s="9"/>
-      <c r="C131" s="9"/>
-      <c r="D131" s="9"/>
-      <c r="E131" s="9"/>
-      <c r="F131" s="9"/>
-      <c r="G131" s="9"/>
-      <c r="H131" s="9"/>
+      <c r="A131" s="10"/>
+      <c r="B131" s="11"/>
+      <c r="C131" s="11"/>
+      <c r="D131" s="11"/>
+      <c r="E131" s="11"/>
+      <c r="F131" s="11"/>
+      <c r="G131" s="11"/>
+      <c r="H131" s="11"/>
       <c r="I131" s="4"/>
       <c r="J131" s="4"/>
       <c r="K131" s="4"/>
@@ -4267,14 +4317,14 @@
       <c r="Z131" s="4"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="8"/>
-      <c r="B132" s="9"/>
-      <c r="C132" s="9"/>
-      <c r="D132" s="9"/>
-      <c r="E132" s="9"/>
-      <c r="F132" s="9"/>
-      <c r="G132" s="9"/>
-      <c r="H132" s="9"/>
+      <c r="A132" s="10"/>
+      <c r="B132" s="11"/>
+      <c r="C132" s="11"/>
+      <c r="D132" s="11"/>
+      <c r="E132" s="11"/>
+      <c r="F132" s="11"/>
+      <c r="G132" s="11"/>
+      <c r="H132" s="11"/>
       <c r="I132" s="4"/>
       <c r="J132" s="4"/>
       <c r="K132" s="4"/>
@@ -4295,14 +4345,14 @@
       <c r="Z132" s="4"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="8"/>
-      <c r="B133" s="9"/>
-      <c r="C133" s="9"/>
-      <c r="D133" s="9"/>
-      <c r="E133" s="9"/>
-      <c r="F133" s="9"/>
-      <c r="G133" s="9"/>
-      <c r="H133" s="9"/>
+      <c r="A133" s="10"/>
+      <c r="B133" s="11"/>
+      <c r="C133" s="11"/>
+      <c r="D133" s="11"/>
+      <c r="E133" s="11"/>
+      <c r="F133" s="11"/>
+      <c r="G133" s="11"/>
+      <c r="H133" s="11"/>
       <c r="I133" s="4"/>
       <c r="J133" s="4"/>
       <c r="K133" s="4"/>
@@ -4323,14 +4373,14 @@
       <c r="Z133" s="4"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="8"/>
-      <c r="B134" s="9"/>
-      <c r="C134" s="9"/>
-      <c r="D134" s="9"/>
-      <c r="E134" s="9"/>
-      <c r="F134" s="9"/>
-      <c r="G134" s="9"/>
-      <c r="H134" s="9"/>
+      <c r="A134" s="10"/>
+      <c r="B134" s="11"/>
+      <c r="C134" s="11"/>
+      <c r="D134" s="11"/>
+      <c r="E134" s="11"/>
+      <c r="F134" s="11"/>
+      <c r="G134" s="11"/>
+      <c r="H134" s="11"/>
       <c r="I134" s="4"/>
       <c r="J134" s="4"/>
       <c r="K134" s="4"/>
@@ -4351,14 +4401,14 @@
       <c r="Z134" s="4"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="8"/>
-      <c r="B135" s="9"/>
-      <c r="C135" s="9"/>
-      <c r="D135" s="9"/>
-      <c r="E135" s="9"/>
-      <c r="F135" s="9"/>
-      <c r="G135" s="9"/>
-      <c r="H135" s="9"/>
+      <c r="A135" s="10"/>
+      <c r="B135" s="11"/>
+      <c r="C135" s="11"/>
+      <c r="D135" s="11"/>
+      <c r="E135" s="11"/>
+      <c r="F135" s="11"/>
+      <c r="G135" s="11"/>
+      <c r="H135" s="11"/>
       <c r="I135" s="4"/>
       <c r="J135" s="4"/>
       <c r="K135" s="4"/>
@@ -4379,14 +4429,14 @@
       <c r="Z135" s="4"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="8"/>
-      <c r="B136" s="9"/>
-      <c r="C136" s="9"/>
-      <c r="D136" s="9"/>
-      <c r="E136" s="9"/>
-      <c r="F136" s="9"/>
-      <c r="G136" s="9"/>
-      <c r="H136" s="9"/>
+      <c r="A136" s="10"/>
+      <c r="B136" s="11"/>
+      <c r="C136" s="11"/>
+      <c r="D136" s="11"/>
+      <c r="E136" s="11"/>
+      <c r="F136" s="11"/>
+      <c r="G136" s="11"/>
+      <c r="H136" s="11"/>
       <c r="I136" s="4"/>
       <c r="J136" s="4"/>
       <c r="K136" s="4"/>
@@ -4407,14 +4457,14 @@
       <c r="Z136" s="4"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="8"/>
-      <c r="B137" s="9"/>
-      <c r="C137" s="9"/>
-      <c r="D137" s="9"/>
-      <c r="E137" s="9"/>
-      <c r="F137" s="9"/>
-      <c r="G137" s="9"/>
-      <c r="H137" s="9"/>
+      <c r="A137" s="10"/>
+      <c r="B137" s="11"/>
+      <c r="C137" s="11"/>
+      <c r="D137" s="11"/>
+      <c r="E137" s="11"/>
+      <c r="F137" s="11"/>
+      <c r="G137" s="11"/>
+      <c r="H137" s="11"/>
       <c r="I137" s="4"/>
       <c r="J137" s="4"/>
       <c r="K137" s="4"/>
@@ -4435,14 +4485,14 @@
       <c r="Z137" s="4"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="8"/>
-      <c r="B138" s="9"/>
-      <c r="C138" s="9"/>
-      <c r="D138" s="9"/>
-      <c r="E138" s="9"/>
-      <c r="F138" s="9"/>
-      <c r="G138" s="9"/>
-      <c r="H138" s="9"/>
+      <c r="A138" s="10"/>
+      <c r="B138" s="11"/>
+      <c r="C138" s="11"/>
+      <c r="D138" s="11"/>
+      <c r="E138" s="11"/>
+      <c r="F138" s="11"/>
+      <c r="G138" s="11"/>
+      <c r="H138" s="11"/>
       <c r="I138" s="4"/>
       <c r="J138" s="4"/>
       <c r="K138" s="4"/>
@@ -4463,14 +4513,14 @@
       <c r="Z138" s="4"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="8"/>
-      <c r="B139" s="9"/>
-      <c r="C139" s="9"/>
-      <c r="D139" s="9"/>
-      <c r="E139" s="9"/>
-      <c r="F139" s="9"/>
-      <c r="G139" s="9"/>
-      <c r="H139" s="9"/>
+      <c r="A139" s="10"/>
+      <c r="B139" s="11"/>
+      <c r="C139" s="11"/>
+      <c r="D139" s="11"/>
+      <c r="E139" s="11"/>
+      <c r="F139" s="11"/>
+      <c r="G139" s="11"/>
+      <c r="H139" s="11"/>
       <c r="I139" s="4"/>
       <c r="J139" s="4"/>
       <c r="K139" s="4"/>
@@ -4491,14 +4541,14 @@
       <c r="Z139" s="4"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="8"/>
-      <c r="B140" s="9"/>
-      <c r="C140" s="9"/>
-      <c r="D140" s="9"/>
-      <c r="E140" s="9"/>
-      <c r="F140" s="9"/>
-      <c r="G140" s="9"/>
-      <c r="H140" s="9"/>
+      <c r="A140" s="10"/>
+      <c r="B140" s="11"/>
+      <c r="C140" s="11"/>
+      <c r="D140" s="11"/>
+      <c r="E140" s="11"/>
+      <c r="F140" s="11"/>
+      <c r="G140" s="11"/>
+      <c r="H140" s="11"/>
       <c r="I140" s="4"/>
       <c r="J140" s="4"/>
       <c r="K140" s="4"/>
@@ -4519,14 +4569,14 @@
       <c r="Z140" s="4"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="8"/>
-      <c r="B141" s="9"/>
-      <c r="C141" s="9"/>
-      <c r="D141" s="9"/>
-      <c r="E141" s="9"/>
-      <c r="F141" s="9"/>
-      <c r="G141" s="9"/>
-      <c r="H141" s="9"/>
+      <c r="A141" s="10"/>
+      <c r="B141" s="11"/>
+      <c r="C141" s="11"/>
+      <c r="D141" s="11"/>
+      <c r="E141" s="11"/>
+      <c r="F141" s="11"/>
+      <c r="G141" s="11"/>
+      <c r="H141" s="11"/>
       <c r="I141" s="4"/>
       <c r="J141" s="4"/>
       <c r="K141" s="4"/>
@@ -4547,14 +4597,14 @@
       <c r="Z141" s="4"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="8"/>
-      <c r="B142" s="9"/>
-      <c r="C142" s="9"/>
-      <c r="D142" s="9"/>
-      <c r="E142" s="9"/>
-      <c r="F142" s="9"/>
-      <c r="G142" s="9"/>
-      <c r="H142" s="9"/>
+      <c r="A142" s="10"/>
+      <c r="B142" s="11"/>
+      <c r="C142" s="11"/>
+      <c r="D142" s="11"/>
+      <c r="E142" s="11"/>
+      <c r="F142" s="11"/>
+      <c r="G142" s="11"/>
+      <c r="H142" s="11"/>
       <c r="I142" s="4"/>
       <c r="J142" s="4"/>
       <c r="K142" s="4"/>
@@ -4575,14 +4625,14 @@
       <c r="Z142" s="4"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="8"/>
-      <c r="B143" s="9"/>
-      <c r="C143" s="9"/>
-      <c r="D143" s="9"/>
-      <c r="E143" s="9"/>
-      <c r="F143" s="9"/>
-      <c r="G143" s="9"/>
-      <c r="H143" s="9"/>
+      <c r="A143" s="10"/>
+      <c r="B143" s="11"/>
+      <c r="C143" s="11"/>
+      <c r="D143" s="11"/>
+      <c r="E143" s="11"/>
+      <c r="F143" s="11"/>
+      <c r="G143" s="11"/>
+      <c r="H143" s="11"/>
       <c r="I143" s="4"/>
       <c r="J143" s="4"/>
       <c r="K143" s="4"/>
@@ -4603,14 +4653,14 @@
       <c r="Z143" s="4"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="8"/>
-      <c r="B144" s="9"/>
-      <c r="C144" s="9"/>
-      <c r="D144" s="9"/>
-      <c r="E144" s="9"/>
-      <c r="F144" s="9"/>
-      <c r="G144" s="9"/>
-      <c r="H144" s="9"/>
+      <c r="A144" s="10"/>
+      <c r="B144" s="11"/>
+      <c r="C144" s="11"/>
+      <c r="D144" s="11"/>
+      <c r="E144" s="11"/>
+      <c r="F144" s="11"/>
+      <c r="G144" s="11"/>
+      <c r="H144" s="11"/>
       <c r="I144" s="4"/>
       <c r="J144" s="4"/>
       <c r="K144" s="4"/>
@@ -4631,14 +4681,14 @@
       <c r="Z144" s="4"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="8"/>
-      <c r="B145" s="9"/>
-      <c r="C145" s="9"/>
-      <c r="D145" s="9"/>
-      <c r="E145" s="9"/>
-      <c r="F145" s="9"/>
-      <c r="G145" s="9"/>
-      <c r="H145" s="9"/>
+      <c r="A145" s="10"/>
+      <c r="B145" s="11"/>
+      <c r="C145" s="11"/>
+      <c r="D145" s="11"/>
+      <c r="E145" s="11"/>
+      <c r="F145" s="11"/>
+      <c r="G145" s="11"/>
+      <c r="H145" s="11"/>
       <c r="I145" s="4"/>
       <c r="J145" s="4"/>
       <c r="K145" s="4"/>
@@ -4659,14 +4709,14 @@
       <c r="Z145" s="4"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="8"/>
-      <c r="B146" s="9"/>
-      <c r="C146" s="9"/>
-      <c r="D146" s="9"/>
-      <c r="E146" s="9"/>
-      <c r="F146" s="9"/>
-      <c r="G146" s="9"/>
-      <c r="H146" s="9"/>
+      <c r="A146" s="10"/>
+      <c r="B146" s="11"/>
+      <c r="C146" s="11"/>
+      <c r="D146" s="11"/>
+      <c r="E146" s="11"/>
+      <c r="F146" s="11"/>
+      <c r="G146" s="11"/>
+      <c r="H146" s="11"/>
       <c r="I146" s="4"/>
       <c r="J146" s="4"/>
       <c r="K146" s="4"/>
@@ -4687,14 +4737,14 @@
       <c r="Z146" s="4"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="8"/>
-      <c r="B147" s="9"/>
-      <c r="C147" s="9"/>
-      <c r="D147" s="9"/>
-      <c r="E147" s="9"/>
-      <c r="F147" s="9"/>
-      <c r="G147" s="9"/>
-      <c r="H147" s="9"/>
+      <c r="A147" s="10"/>
+      <c r="B147" s="11"/>
+      <c r="C147" s="11"/>
+      <c r="D147" s="11"/>
+      <c r="E147" s="11"/>
+      <c r="F147" s="11"/>
+      <c r="G147" s="11"/>
+      <c r="H147" s="11"/>
       <c r="I147" s="4"/>
       <c r="J147" s="4"/>
       <c r="K147" s="4"/>
@@ -4715,14 +4765,14 @@
       <c r="Z147" s="4"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="8"/>
-      <c r="B148" s="9"/>
-      <c r="C148" s="9"/>
-      <c r="D148" s="9"/>
-      <c r="E148" s="9"/>
-      <c r="F148" s="9"/>
-      <c r="G148" s="9"/>
-      <c r="H148" s="9"/>
+      <c r="A148" s="10"/>
+      <c r="B148" s="11"/>
+      <c r="C148" s="11"/>
+      <c r="D148" s="11"/>
+      <c r="E148" s="11"/>
+      <c r="F148" s="11"/>
+      <c r="G148" s="11"/>
+      <c r="H148" s="11"/>
       <c r="I148" s="4"/>
       <c r="J148" s="4"/>
       <c r="K148" s="4"/>
@@ -4743,14 +4793,14 @@
       <c r="Z148" s="4"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="8"/>
-      <c r="B149" s="9"/>
-      <c r="C149" s="9"/>
-      <c r="D149" s="9"/>
-      <c r="E149" s="9"/>
-      <c r="F149" s="9"/>
-      <c r="G149" s="9"/>
-      <c r="H149" s="9"/>
+      <c r="A149" s="10"/>
+      <c r="B149" s="11"/>
+      <c r="C149" s="11"/>
+      <c r="D149" s="11"/>
+      <c r="E149" s="11"/>
+      <c r="F149" s="11"/>
+      <c r="G149" s="11"/>
+      <c r="H149" s="11"/>
       <c r="I149" s="4"/>
       <c r="J149" s="4"/>
       <c r="K149" s="4"/>
@@ -4771,14 +4821,14 @@
       <c r="Z149" s="4"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="8"/>
-      <c r="B150" s="9"/>
-      <c r="C150" s="9"/>
-      <c r="D150" s="9"/>
-      <c r="E150" s="9"/>
-      <c r="F150" s="9"/>
-      <c r="G150" s="9"/>
-      <c r="H150" s="9"/>
+      <c r="A150" s="10"/>
+      <c r="B150" s="11"/>
+      <c r="C150" s="11"/>
+      <c r="D150" s="11"/>
+      <c r="E150" s="11"/>
+      <c r="F150" s="11"/>
+      <c r="G150" s="11"/>
+      <c r="H150" s="11"/>
       <c r="I150" s="4"/>
       <c r="J150" s="4"/>
       <c r="K150" s="4"/>
@@ -4799,14 +4849,14 @@
       <c r="Z150" s="4"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="8"/>
-      <c r="B151" s="9"/>
-      <c r="C151" s="9"/>
-      <c r="D151" s="9"/>
-      <c r="E151" s="9"/>
-      <c r="F151" s="9"/>
-      <c r="G151" s="9"/>
-      <c r="H151" s="9"/>
+      <c r="A151" s="10"/>
+      <c r="B151" s="11"/>
+      <c r="C151" s="11"/>
+      <c r="D151" s="11"/>
+      <c r="E151" s="11"/>
+      <c r="F151" s="11"/>
+      <c r="G151" s="11"/>
+      <c r="H151" s="11"/>
       <c r="I151" s="4"/>
       <c r="J151" s="4"/>
       <c r="K151" s="4"/>
@@ -4827,14 +4877,14 @@
       <c r="Z151" s="4"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="8"/>
-      <c r="B152" s="9"/>
-      <c r="C152" s="9"/>
-      <c r="D152" s="9"/>
-      <c r="E152" s="9"/>
-      <c r="F152" s="9"/>
-      <c r="G152" s="9"/>
-      <c r="H152" s="9"/>
+      <c r="A152" s="10"/>
+      <c r="B152" s="11"/>
+      <c r="C152" s="11"/>
+      <c r="D152" s="11"/>
+      <c r="E152" s="11"/>
+      <c r="F152" s="11"/>
+      <c r="G152" s="11"/>
+      <c r="H152" s="11"/>
       <c r="I152" s="4"/>
       <c r="J152" s="4"/>
       <c r="K152" s="4"/>
@@ -4855,14 +4905,14 @@
       <c r="Z152" s="4"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="8"/>
-      <c r="B153" s="9"/>
-      <c r="C153" s="9"/>
-      <c r="D153" s="9"/>
-      <c r="E153" s="9"/>
-      <c r="F153" s="9"/>
-      <c r="G153" s="9"/>
-      <c r="H153" s="9"/>
+      <c r="A153" s="10"/>
+      <c r="B153" s="11"/>
+      <c r="C153" s="11"/>
+      <c r="D153" s="11"/>
+      <c r="E153" s="11"/>
+      <c r="F153" s="11"/>
+      <c r="G153" s="11"/>
+      <c r="H153" s="11"/>
       <c r="I153" s="4"/>
       <c r="J153" s="4"/>
       <c r="K153" s="4"/>
@@ -4883,14 +4933,14 @@
       <c r="Z153" s="4"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="8"/>
-      <c r="B154" s="9"/>
-      <c r="C154" s="9"/>
-      <c r="D154" s="9"/>
-      <c r="E154" s="9"/>
-      <c r="F154" s="9"/>
-      <c r="G154" s="9"/>
-      <c r="H154" s="9"/>
+      <c r="A154" s="10"/>
+      <c r="B154" s="11"/>
+      <c r="C154" s="11"/>
+      <c r="D154" s="11"/>
+      <c r="E154" s="11"/>
+      <c r="F154" s="11"/>
+      <c r="G154" s="11"/>
+      <c r="H154" s="11"/>
       <c r="I154" s="4"/>
       <c r="J154" s="4"/>
       <c r="K154" s="4"/>
@@ -4911,14 +4961,14 @@
       <c r="Z154" s="4"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="8"/>
-      <c r="B155" s="9"/>
-      <c r="C155" s="9"/>
-      <c r="D155" s="9"/>
-      <c r="E155" s="9"/>
-      <c r="F155" s="9"/>
-      <c r="G155" s="9"/>
-      <c r="H155" s="9"/>
+      <c r="A155" s="10"/>
+      <c r="B155" s="11"/>
+      <c r="C155" s="11"/>
+      <c r="D155" s="11"/>
+      <c r="E155" s="11"/>
+      <c r="F155" s="11"/>
+      <c r="G155" s="11"/>
+      <c r="H155" s="11"/>
       <c r="I155" s="4"/>
       <c r="J155" s="4"/>
       <c r="K155" s="4"/>
@@ -4939,14 +4989,14 @@
       <c r="Z155" s="4"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="8"/>
-      <c r="B156" s="9"/>
-      <c r="C156" s="9"/>
-      <c r="D156" s="9"/>
-      <c r="E156" s="9"/>
-      <c r="F156" s="9"/>
-      <c r="G156" s="9"/>
-      <c r="H156" s="9"/>
+      <c r="A156" s="10"/>
+      <c r="B156" s="11"/>
+      <c r="C156" s="11"/>
+      <c r="D156" s="11"/>
+      <c r="E156" s="11"/>
+      <c r="F156" s="11"/>
+      <c r="G156" s="11"/>
+      <c r="H156" s="11"/>
       <c r="I156" s="4"/>
       <c r="J156" s="4"/>
       <c r="K156" s="4"/>
@@ -4967,14 +5017,14 @@
       <c r="Z156" s="4"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="A157" s="8"/>
-      <c r="B157" s="9"/>
-      <c r="C157" s="9"/>
-      <c r="D157" s="9"/>
-      <c r="E157" s="9"/>
-      <c r="F157" s="9"/>
-      <c r="G157" s="9"/>
-      <c r="H157" s="9"/>
+      <c r="A157" s="10"/>
+      <c r="B157" s="11"/>
+      <c r="C157" s="11"/>
+      <c r="D157" s="11"/>
+      <c r="E157" s="11"/>
+      <c r="F157" s="11"/>
+      <c r="G157" s="11"/>
+      <c r="H157" s="11"/>
       <c r="I157" s="4"/>
       <c r="J157" s="4"/>
       <c r="K157" s="4"/>
@@ -4995,14 +5045,14 @@
       <c r="Z157" s="4"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="A158" s="8"/>
-      <c r="B158" s="9"/>
-      <c r="C158" s="9"/>
-      <c r="D158" s="9"/>
-      <c r="E158" s="9"/>
-      <c r="F158" s="9"/>
-      <c r="G158" s="9"/>
-      <c r="H158" s="9"/>
+      <c r="A158" s="10"/>
+      <c r="B158" s="11"/>
+      <c r="C158" s="11"/>
+      <c r="D158" s="11"/>
+      <c r="E158" s="11"/>
+      <c r="F158" s="11"/>
+      <c r="G158" s="11"/>
+      <c r="H158" s="11"/>
       <c r="I158" s="4"/>
       <c r="J158" s="4"/>
       <c r="K158" s="4"/>
@@ -5023,14 +5073,14 @@
       <c r="Z158" s="4"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="A159" s="8"/>
-      <c r="B159" s="9"/>
-      <c r="C159" s="9"/>
-      <c r="D159" s="9"/>
-      <c r="E159" s="9"/>
-      <c r="F159" s="9"/>
-      <c r="G159" s="9"/>
-      <c r="H159" s="9"/>
+      <c r="A159" s="10"/>
+      <c r="B159" s="11"/>
+      <c r="C159" s="11"/>
+      <c r="D159" s="11"/>
+      <c r="E159" s="11"/>
+      <c r="F159" s="11"/>
+      <c r="G159" s="11"/>
+      <c r="H159" s="11"/>
       <c r="I159" s="4"/>
       <c r="J159" s="4"/>
       <c r="K159" s="4"/>
@@ -5051,14 +5101,14 @@
       <c r="Z159" s="4"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="A160" s="8"/>
-      <c r="B160" s="9"/>
-      <c r="C160" s="9"/>
-      <c r="D160" s="9"/>
-      <c r="E160" s="9"/>
-      <c r="F160" s="9"/>
-      <c r="G160" s="9"/>
-      <c r="H160" s="9"/>
+      <c r="A160" s="10"/>
+      <c r="B160" s="11"/>
+      <c r="C160" s="11"/>
+      <c r="D160" s="11"/>
+      <c r="E160" s="11"/>
+      <c r="F160" s="11"/>
+      <c r="G160" s="11"/>
+      <c r="H160" s="11"/>
       <c r="I160" s="4"/>
       <c r="J160" s="4"/>
       <c r="K160" s="4"/>
@@ -5079,14 +5129,14 @@
       <c r="Z160" s="4"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="A161" s="8"/>
-      <c r="B161" s="9"/>
-      <c r="C161" s="9"/>
-      <c r="D161" s="9"/>
-      <c r="E161" s="9"/>
-      <c r="F161" s="9"/>
-      <c r="G161" s="9"/>
-      <c r="H161" s="9"/>
+      <c r="A161" s="10"/>
+      <c r="B161" s="11"/>
+      <c r="C161" s="11"/>
+      <c r="D161" s="11"/>
+      <c r="E161" s="11"/>
+      <c r="F161" s="11"/>
+      <c r="G161" s="11"/>
+      <c r="H161" s="11"/>
       <c r="I161" s="4"/>
       <c r="J161" s="4"/>
       <c r="K161" s="4"/>
@@ -5107,14 +5157,14 @@
       <c r="Z161" s="4"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="A162" s="8"/>
-      <c r="B162" s="9"/>
-      <c r="C162" s="9"/>
-      <c r="D162" s="9"/>
-      <c r="E162" s="9"/>
-      <c r="F162" s="9"/>
-      <c r="G162" s="9"/>
-      <c r="H162" s="9"/>
+      <c r="A162" s="10"/>
+      <c r="B162" s="11"/>
+      <c r="C162" s="11"/>
+      <c r="D162" s="11"/>
+      <c r="E162" s="11"/>
+      <c r="F162" s="11"/>
+      <c r="G162" s="11"/>
+      <c r="H162" s="11"/>
       <c r="I162" s="4"/>
       <c r="J162" s="4"/>
       <c r="K162" s="4"/>
@@ -5135,14 +5185,14 @@
       <c r="Z162" s="4"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="A163" s="8"/>
-      <c r="B163" s="9"/>
-      <c r="C163" s="9"/>
-      <c r="D163" s="9"/>
-      <c r="E163" s="9"/>
-      <c r="F163" s="9"/>
-      <c r="G163" s="9"/>
-      <c r="H163" s="9"/>
+      <c r="A163" s="10"/>
+      <c r="B163" s="11"/>
+      <c r="C163" s="11"/>
+      <c r="D163" s="11"/>
+      <c r="E163" s="11"/>
+      <c r="F163" s="11"/>
+      <c r="G163" s="11"/>
+      <c r="H163" s="11"/>
       <c r="I163" s="4"/>
       <c r="J163" s="4"/>
       <c r="K163" s="4"/>
@@ -5163,14 +5213,14 @@
       <c r="Z163" s="4"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="A164" s="8"/>
-      <c r="B164" s="9"/>
-      <c r="C164" s="9"/>
-      <c r="D164" s="9"/>
-      <c r="E164" s="9"/>
-      <c r="F164" s="9"/>
-      <c r="G164" s="9"/>
-      <c r="H164" s="9"/>
+      <c r="A164" s="10"/>
+      <c r="B164" s="11"/>
+      <c r="C164" s="11"/>
+      <c r="D164" s="11"/>
+      <c r="E164" s="11"/>
+      <c r="F164" s="11"/>
+      <c r="G164" s="11"/>
+      <c r="H164" s="11"/>
       <c r="I164" s="4"/>
       <c r="J164" s="4"/>
       <c r="K164" s="4"/>
@@ -5191,14 +5241,14 @@
       <c r="Z164" s="4"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="8"/>
-      <c r="B165" s="9"/>
-      <c r="C165" s="9"/>
-      <c r="D165" s="9"/>
-      <c r="E165" s="9"/>
-      <c r="F165" s="9"/>
-      <c r="G165" s="9"/>
-      <c r="H165" s="9"/>
+      <c r="A165" s="10"/>
+      <c r="B165" s="11"/>
+      <c r="C165" s="11"/>
+      <c r="D165" s="11"/>
+      <c r="E165" s="11"/>
+      <c r="F165" s="11"/>
+      <c r="G165" s="11"/>
+      <c r="H165" s="11"/>
       <c r="I165" s="4"/>
       <c r="J165" s="4"/>
       <c r="K165" s="4"/>
@@ -5219,14 +5269,14 @@
       <c r="Z165" s="4"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="A166" s="8"/>
-      <c r="B166" s="9"/>
-      <c r="C166" s="9"/>
-      <c r="D166" s="9"/>
-      <c r="E166" s="9"/>
-      <c r="F166" s="9"/>
-      <c r="G166" s="9"/>
-      <c r="H166" s="9"/>
+      <c r="A166" s="10"/>
+      <c r="B166" s="11"/>
+      <c r="C166" s="11"/>
+      <c r="D166" s="11"/>
+      <c r="E166" s="11"/>
+      <c r="F166" s="11"/>
+      <c r="G166" s="11"/>
+      <c r="H166" s="11"/>
       <c r="I166" s="4"/>
       <c r="J166" s="4"/>
       <c r="K166" s="4"/>
@@ -5247,14 +5297,14 @@
       <c r="Z166" s="4"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="A167" s="8"/>
-      <c r="B167" s="9"/>
-      <c r="C167" s="9"/>
-      <c r="D167" s="9"/>
-      <c r="E167" s="9"/>
-      <c r="F167" s="9"/>
-      <c r="G167" s="9"/>
-      <c r="H167" s="9"/>
+      <c r="A167" s="10"/>
+      <c r="B167" s="11"/>
+      <c r="C167" s="11"/>
+      <c r="D167" s="11"/>
+      <c r="E167" s="11"/>
+      <c r="F167" s="11"/>
+      <c r="G167" s="11"/>
+      <c r="H167" s="11"/>
       <c r="I167" s="4"/>
       <c r="J167" s="4"/>
       <c r="K167" s="4"/>
@@ -5275,14 +5325,14 @@
       <c r="Z167" s="4"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
-      <c r="A168" s="8"/>
-      <c r="B168" s="9"/>
-      <c r="C168" s="9"/>
-      <c r="D168" s="9"/>
-      <c r="E168" s="9"/>
-      <c r="F168" s="9"/>
-      <c r="G168" s="9"/>
-      <c r="H168" s="9"/>
+      <c r="A168" s="10"/>
+      <c r="B168" s="11"/>
+      <c r="C168" s="11"/>
+      <c r="D168" s="11"/>
+      <c r="E168" s="11"/>
+      <c r="F168" s="11"/>
+      <c r="G168" s="11"/>
+      <c r="H168" s="11"/>
       <c r="I168" s="4"/>
       <c r="J168" s="4"/>
       <c r="K168" s="4"/>
@@ -5303,14 +5353,14 @@
       <c r="Z168" s="4"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="A169" s="8"/>
-      <c r="B169" s="9"/>
-      <c r="C169" s="9"/>
-      <c r="D169" s="9"/>
-      <c r="E169" s="9"/>
-      <c r="F169" s="9"/>
-      <c r="G169" s="9"/>
-      <c r="H169" s="9"/>
+      <c r="A169" s="10"/>
+      <c r="B169" s="11"/>
+      <c r="C169" s="11"/>
+      <c r="D169" s="11"/>
+      <c r="E169" s="11"/>
+      <c r="F169" s="11"/>
+      <c r="G169" s="11"/>
+      <c r="H169" s="11"/>
       <c r="I169" s="4"/>
       <c r="J169" s="4"/>
       <c r="K169" s="4"/>
@@ -5331,14 +5381,14 @@
       <c r="Z169" s="4"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="A170" s="8"/>
-      <c r="B170" s="9"/>
-      <c r="C170" s="9"/>
-      <c r="D170" s="9"/>
-      <c r="E170" s="9"/>
-      <c r="F170" s="9"/>
-      <c r="G170" s="9"/>
-      <c r="H170" s="9"/>
+      <c r="A170" s="10"/>
+      <c r="B170" s="11"/>
+      <c r="C170" s="11"/>
+      <c r="D170" s="11"/>
+      <c r="E170" s="11"/>
+      <c r="F170" s="11"/>
+      <c r="G170" s="11"/>
+      <c r="H170" s="11"/>
       <c r="I170" s="4"/>
       <c r="J170" s="4"/>
       <c r="K170" s="4"/>
@@ -5359,14 +5409,14 @@
       <c r="Z170" s="4"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="A171" s="8"/>
-      <c r="B171" s="9"/>
-      <c r="C171" s="9"/>
-      <c r="D171" s="9"/>
-      <c r="E171" s="9"/>
-      <c r="F171" s="9"/>
-      <c r="G171" s="9"/>
-      <c r="H171" s="9"/>
+      <c r="A171" s="10"/>
+      <c r="B171" s="11"/>
+      <c r="C171" s="11"/>
+      <c r="D171" s="11"/>
+      <c r="E171" s="11"/>
+      <c r="F171" s="11"/>
+      <c r="G171" s="11"/>
+      <c r="H171" s="11"/>
       <c r="I171" s="4"/>
       <c r="J171" s="4"/>
       <c r="K171" s="4"/>
@@ -5387,14 +5437,14 @@
       <c r="Z171" s="4"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="A172" s="8"/>
-      <c r="B172" s="9"/>
-      <c r="C172" s="9"/>
-      <c r="D172" s="9"/>
-      <c r="E172" s="9"/>
-      <c r="F172" s="9"/>
-      <c r="G172" s="9"/>
-      <c r="H172" s="9"/>
+      <c r="A172" s="10"/>
+      <c r="B172" s="11"/>
+      <c r="C172" s="11"/>
+      <c r="D172" s="11"/>
+      <c r="E172" s="11"/>
+      <c r="F172" s="11"/>
+      <c r="G172" s="11"/>
+      <c r="H172" s="11"/>
       <c r="I172" s="4"/>
       <c r="J172" s="4"/>
       <c r="K172" s="4"/>
@@ -5415,14 +5465,14 @@
       <c r="Z172" s="4"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="A173" s="8"/>
-      <c r="B173" s="9"/>
-      <c r="C173" s="9"/>
-      <c r="D173" s="9"/>
-      <c r="E173" s="9"/>
-      <c r="F173" s="9"/>
-      <c r="G173" s="9"/>
-      <c r="H173" s="9"/>
+      <c r="A173" s="10"/>
+      <c r="B173" s="11"/>
+      <c r="C173" s="11"/>
+      <c r="D173" s="11"/>
+      <c r="E173" s="11"/>
+      <c r="F173" s="11"/>
+      <c r="G173" s="11"/>
+      <c r="H173" s="11"/>
       <c r="I173" s="4"/>
       <c r="J173" s="4"/>
       <c r="K173" s="4"/>
@@ -5443,14 +5493,14 @@
       <c r="Z173" s="4"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="A174" s="8"/>
-      <c r="B174" s="9"/>
-      <c r="C174" s="9"/>
-      <c r="D174" s="9"/>
-      <c r="E174" s="9"/>
-      <c r="F174" s="9"/>
-      <c r="G174" s="9"/>
-      <c r="H174" s="9"/>
+      <c r="A174" s="10"/>
+      <c r="B174" s="11"/>
+      <c r="C174" s="11"/>
+      <c r="D174" s="11"/>
+      <c r="E174" s="11"/>
+      <c r="F174" s="11"/>
+      <c r="G174" s="11"/>
+      <c r="H174" s="11"/>
       <c r="I174" s="4"/>
       <c r="J174" s="4"/>
       <c r="K174" s="4"/>
@@ -5471,14 +5521,14 @@
       <c r="Z174" s="4"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="A175" s="8"/>
-      <c r="B175" s="9"/>
-      <c r="C175" s="9"/>
-      <c r="D175" s="9"/>
-      <c r="E175" s="9"/>
-      <c r="F175" s="9"/>
-      <c r="G175" s="9"/>
-      <c r="H175" s="9"/>
+      <c r="A175" s="10"/>
+      <c r="B175" s="11"/>
+      <c r="C175" s="11"/>
+      <c r="D175" s="11"/>
+      <c r="E175" s="11"/>
+      <c r="F175" s="11"/>
+      <c r="G175" s="11"/>
+      <c r="H175" s="11"/>
       <c r="I175" s="4"/>
       <c r="J175" s="4"/>
       <c r="K175" s="4"/>
@@ -5499,14 +5549,14 @@
       <c r="Z175" s="4"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
-      <c r="A176" s="8"/>
-      <c r="B176" s="9"/>
-      <c r="C176" s="9"/>
-      <c r="D176" s="9"/>
-      <c r="E176" s="9"/>
-      <c r="F176" s="9"/>
-      <c r="G176" s="9"/>
-      <c r="H176" s="9"/>
+      <c r="A176" s="10"/>
+      <c r="B176" s="11"/>
+      <c r="C176" s="11"/>
+      <c r="D176" s="11"/>
+      <c r="E176" s="11"/>
+      <c r="F176" s="11"/>
+      <c r="G176" s="11"/>
+      <c r="H176" s="11"/>
       <c r="I176" s="4"/>
       <c r="J176" s="4"/>
       <c r="K176" s="4"/>
@@ -5527,14 +5577,14 @@
       <c r="Z176" s="4"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="A177" s="8"/>
-      <c r="B177" s="9"/>
-      <c r="C177" s="9"/>
-      <c r="D177" s="9"/>
-      <c r="E177" s="9"/>
-      <c r="F177" s="9"/>
-      <c r="G177" s="9"/>
-      <c r="H177" s="9"/>
+      <c r="A177" s="10"/>
+      <c r="B177" s="11"/>
+      <c r="C177" s="11"/>
+      <c r="D177" s="11"/>
+      <c r="E177" s="11"/>
+      <c r="F177" s="11"/>
+      <c r="G177" s="11"/>
+      <c r="H177" s="11"/>
       <c r="I177" s="4"/>
       <c r="J177" s="4"/>
       <c r="K177" s="4"/>
@@ -5555,14 +5605,14 @@
       <c r="Z177" s="4"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
-      <c r="A178" s="8"/>
-      <c r="B178" s="9"/>
-      <c r="C178" s="9"/>
-      <c r="D178" s="9"/>
-      <c r="E178" s="9"/>
-      <c r="F178" s="9"/>
-      <c r="G178" s="9"/>
-      <c r="H178" s="9"/>
+      <c r="A178" s="10"/>
+      <c r="B178" s="11"/>
+      <c r="C178" s="11"/>
+      <c r="D178" s="11"/>
+      <c r="E178" s="11"/>
+      <c r="F178" s="11"/>
+      <c r="G178" s="11"/>
+      <c r="H178" s="11"/>
       <c r="I178" s="4"/>
       <c r="J178" s="4"/>
       <c r="K178" s="4"/>
@@ -5583,14 +5633,14 @@
       <c r="Z178" s="4"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="A179" s="8"/>
-      <c r="B179" s="9"/>
-      <c r="C179" s="9"/>
-      <c r="D179" s="9"/>
-      <c r="E179" s="9"/>
-      <c r="F179" s="9"/>
-      <c r="G179" s="9"/>
-      <c r="H179" s="9"/>
+      <c r="A179" s="10"/>
+      <c r="B179" s="11"/>
+      <c r="C179" s="11"/>
+      <c r="D179" s="11"/>
+      <c r="E179" s="11"/>
+      <c r="F179" s="11"/>
+      <c r="G179" s="11"/>
+      <c r="H179" s="11"/>
       <c r="I179" s="4"/>
       <c r="J179" s="4"/>
       <c r="K179" s="4"/>
@@ -5611,14 +5661,14 @@
       <c r="Z179" s="4"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
-      <c r="A180" s="8"/>
-      <c r="B180" s="9"/>
-      <c r="C180" s="9"/>
-      <c r="D180" s="9"/>
-      <c r="E180" s="9"/>
-      <c r="F180" s="9"/>
-      <c r="G180" s="9"/>
-      <c r="H180" s="9"/>
+      <c r="A180" s="10"/>
+      <c r="B180" s="11"/>
+      <c r="C180" s="11"/>
+      <c r="D180" s="11"/>
+      <c r="E180" s="11"/>
+      <c r="F180" s="11"/>
+      <c r="G180" s="11"/>
+      <c r="H180" s="11"/>
       <c r="I180" s="4"/>
       <c r="J180" s="4"/>
       <c r="K180" s="4"/>
@@ -5639,14 +5689,14 @@
       <c r="Z180" s="4"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
-      <c r="A181" s="8"/>
-      <c r="B181" s="9"/>
-      <c r="C181" s="9"/>
-      <c r="D181" s="9"/>
-      <c r="E181" s="9"/>
-      <c r="F181" s="9"/>
-      <c r="G181" s="9"/>
-      <c r="H181" s="9"/>
+      <c r="A181" s="10"/>
+      <c r="B181" s="11"/>
+      <c r="C181" s="11"/>
+      <c r="D181" s="11"/>
+      <c r="E181" s="11"/>
+      <c r="F181" s="11"/>
+      <c r="G181" s="11"/>
+      <c r="H181" s="11"/>
       <c r="I181" s="4"/>
       <c r="J181" s="4"/>
       <c r="K181" s="4"/>
@@ -5667,14 +5717,14 @@
       <c r="Z181" s="4"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
-      <c r="A182" s="8"/>
-      <c r="B182" s="9"/>
-      <c r="C182" s="9"/>
-      <c r="D182" s="9"/>
-      <c r="E182" s="9"/>
-      <c r="F182" s="9"/>
-      <c r="G182" s="9"/>
-      <c r="H182" s="9"/>
+      <c r="A182" s="10"/>
+      <c r="B182" s="11"/>
+      <c r="C182" s="11"/>
+      <c r="D182" s="11"/>
+      <c r="E182" s="11"/>
+      <c r="F182" s="11"/>
+      <c r="G182" s="11"/>
+      <c r="H182" s="11"/>
       <c r="I182" s="4"/>
       <c r="J182" s="4"/>
       <c r="K182" s="4"/>
@@ -5695,14 +5745,14 @@
       <c r="Z182" s="4"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
-      <c r="A183" s="8"/>
-      <c r="B183" s="9"/>
-      <c r="C183" s="9"/>
-      <c r="D183" s="9"/>
-      <c r="E183" s="9"/>
-      <c r="F183" s="9"/>
-      <c r="G183" s="9"/>
-      <c r="H183" s="9"/>
+      <c r="A183" s="10"/>
+      <c r="B183" s="11"/>
+      <c r="C183" s="11"/>
+      <c r="D183" s="11"/>
+      <c r="E183" s="11"/>
+      <c r="F183" s="11"/>
+      <c r="G183" s="11"/>
+      <c r="H183" s="11"/>
       <c r="I183" s="4"/>
       <c r="J183" s="4"/>
       <c r="K183" s="4"/>
@@ -5723,14 +5773,14 @@
       <c r="Z183" s="4"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
-      <c r="A184" s="8"/>
-      <c r="B184" s="9"/>
-      <c r="C184" s="9"/>
-      <c r="D184" s="9"/>
-      <c r="E184" s="9"/>
-      <c r="F184" s="9"/>
-      <c r="G184" s="9"/>
-      <c r="H184" s="9"/>
+      <c r="A184" s="10"/>
+      <c r="B184" s="11"/>
+      <c r="C184" s="11"/>
+      <c r="D184" s="11"/>
+      <c r="E184" s="11"/>
+      <c r="F184" s="11"/>
+      <c r="G184" s="11"/>
+      <c r="H184" s="11"/>
       <c r="I184" s="4"/>
       <c r="J184" s="4"/>
       <c r="K184" s="4"/>
@@ -5751,14 +5801,14 @@
       <c r="Z184" s="4"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
-      <c r="A185" s="8"/>
-      <c r="B185" s="9"/>
-      <c r="C185" s="9"/>
-      <c r="D185" s="9"/>
-      <c r="E185" s="9"/>
-      <c r="F185" s="9"/>
-      <c r="G185" s="9"/>
-      <c r="H185" s="9"/>
+      <c r="A185" s="10"/>
+      <c r="B185" s="11"/>
+      <c r="C185" s="11"/>
+      <c r="D185" s="11"/>
+      <c r="E185" s="11"/>
+      <c r="F185" s="11"/>
+      <c r="G185" s="11"/>
+      <c r="H185" s="11"/>
       <c r="I185" s="4"/>
       <c r="J185" s="4"/>
       <c r="K185" s="4"/>
@@ -5779,14 +5829,14 @@
       <c r="Z185" s="4"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
-      <c r="A186" s="8"/>
-      <c r="B186" s="9"/>
-      <c r="C186" s="9"/>
-      <c r="D186" s="9"/>
-      <c r="E186" s="9"/>
-      <c r="F186" s="9"/>
-      <c r="G186" s="9"/>
-      <c r="H186" s="9"/>
+      <c r="A186" s="10"/>
+      <c r="B186" s="11"/>
+      <c r="C186" s="11"/>
+      <c r="D186" s="11"/>
+      <c r="E186" s="11"/>
+      <c r="F186" s="11"/>
+      <c r="G186" s="11"/>
+      <c r="H186" s="11"/>
       <c r="I186" s="4"/>
       <c r="J186" s="4"/>
       <c r="K186" s="4"/>
@@ -5807,14 +5857,14 @@
       <c r="Z186" s="4"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
-      <c r="A187" s="8"/>
-      <c r="B187" s="9"/>
-      <c r="C187" s="9"/>
-      <c r="D187" s="9"/>
-      <c r="E187" s="9"/>
-      <c r="F187" s="9"/>
-      <c r="G187" s="9"/>
-      <c r="H187" s="9"/>
+      <c r="A187" s="10"/>
+      <c r="B187" s="11"/>
+      <c r="C187" s="11"/>
+      <c r="D187" s="11"/>
+      <c r="E187" s="11"/>
+      <c r="F187" s="11"/>
+      <c r="G187" s="11"/>
+      <c r="H187" s="11"/>
       <c r="I187" s="4"/>
       <c r="J187" s="4"/>
       <c r="K187" s="4"/>
@@ -5835,14 +5885,14 @@
       <c r="Z187" s="4"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
-      <c r="A188" s="8"/>
-      <c r="B188" s="9"/>
-      <c r="C188" s="9"/>
-      <c r="D188" s="9"/>
-      <c r="E188" s="9"/>
-      <c r="F188" s="9"/>
-      <c r="G188" s="9"/>
-      <c r="H188" s="9"/>
+      <c r="A188" s="10"/>
+      <c r="B188" s="11"/>
+      <c r="C188" s="11"/>
+      <c r="D188" s="11"/>
+      <c r="E188" s="11"/>
+      <c r="F188" s="11"/>
+      <c r="G188" s="11"/>
+      <c r="H188" s="11"/>
       <c r="I188" s="4"/>
       <c r="J188" s="4"/>
       <c r="K188" s="4"/>
@@ -5863,14 +5913,14 @@
       <c r="Z188" s="4"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
-      <c r="A189" s="8"/>
-      <c r="B189" s="9"/>
-      <c r="C189" s="9"/>
-      <c r="D189" s="9"/>
-      <c r="E189" s="9"/>
-      <c r="F189" s="9"/>
-      <c r="G189" s="9"/>
-      <c r="H189" s="9"/>
+      <c r="A189" s="10"/>
+      <c r="B189" s="11"/>
+      <c r="C189" s="11"/>
+      <c r="D189" s="11"/>
+      <c r="E189" s="11"/>
+      <c r="F189" s="11"/>
+      <c r="G189" s="11"/>
+      <c r="H189" s="11"/>
       <c r="I189" s="4"/>
       <c r="J189" s="4"/>
       <c r="K189" s="4"/>
@@ -5891,14 +5941,14 @@
       <c r="Z189" s="4"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
-      <c r="A190" s="8"/>
-      <c r="B190" s="9"/>
-      <c r="C190" s="9"/>
-      <c r="D190" s="9"/>
-      <c r="E190" s="9"/>
-      <c r="F190" s="9"/>
-      <c r="G190" s="9"/>
-      <c r="H190" s="9"/>
+      <c r="A190" s="10"/>
+      <c r="B190" s="11"/>
+      <c r="C190" s="11"/>
+      <c r="D190" s="11"/>
+      <c r="E190" s="11"/>
+      <c r="F190" s="11"/>
+      <c r="G190" s="11"/>
+      <c r="H190" s="11"/>
       <c r="I190" s="4"/>
       <c r="J190" s="4"/>
       <c r="K190" s="4"/>
@@ -5919,14 +5969,14 @@
       <c r="Z190" s="4"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
-      <c r="A191" s="8"/>
-      <c r="B191" s="9"/>
-      <c r="C191" s="9"/>
-      <c r="D191" s="9"/>
-      <c r="E191" s="9"/>
-      <c r="F191" s="9"/>
-      <c r="G191" s="9"/>
-      <c r="H191" s="9"/>
+      <c r="A191" s="10"/>
+      <c r="B191" s="11"/>
+      <c r="C191" s="11"/>
+      <c r="D191" s="11"/>
+      <c r="E191" s="11"/>
+      <c r="F191" s="11"/>
+      <c r="G191" s="11"/>
+      <c r="H191" s="11"/>
       <c r="I191" s="4"/>
       <c r="J191" s="4"/>
       <c r="K191" s="4"/>
@@ -5947,14 +5997,14 @@
       <c r="Z191" s="4"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
-      <c r="A192" s="8"/>
-      <c r="B192" s="9"/>
-      <c r="C192" s="9"/>
-      <c r="D192" s="9"/>
-      <c r="E192" s="9"/>
-      <c r="F192" s="9"/>
-      <c r="G192" s="9"/>
-      <c r="H192" s="9"/>
+      <c r="A192" s="10"/>
+      <c r="B192" s="11"/>
+      <c r="C192" s="11"/>
+      <c r="D192" s="11"/>
+      <c r="E192" s="11"/>
+      <c r="F192" s="11"/>
+      <c r="G192" s="11"/>
+      <c r="H192" s="11"/>
       <c r="I192" s="4"/>
       <c r="J192" s="4"/>
       <c r="K192" s="4"/>
@@ -5975,14 +6025,14 @@
       <c r="Z192" s="4"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
-      <c r="A193" s="8"/>
-      <c r="B193" s="9"/>
-      <c r="C193" s="9"/>
-      <c r="D193" s="9"/>
-      <c r="E193" s="9"/>
-      <c r="F193" s="9"/>
-      <c r="G193" s="9"/>
-      <c r="H193" s="9"/>
+      <c r="A193" s="10"/>
+      <c r="B193" s="11"/>
+      <c r="C193" s="11"/>
+      <c r="D193" s="11"/>
+      <c r="E193" s="11"/>
+      <c r="F193" s="11"/>
+      <c r="G193" s="11"/>
+      <c r="H193" s="11"/>
       <c r="I193" s="4"/>
       <c r="J193" s="4"/>
       <c r="K193" s="4"/>
@@ -6003,14 +6053,14 @@
       <c r="Z193" s="4"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="A194" s="8"/>
-      <c r="B194" s="9"/>
-      <c r="C194" s="9"/>
-      <c r="D194" s="9"/>
-      <c r="E194" s="9"/>
-      <c r="F194" s="9"/>
-      <c r="G194" s="9"/>
-      <c r="H194" s="9"/>
+      <c r="A194" s="10"/>
+      <c r="B194" s="11"/>
+      <c r="C194" s="11"/>
+      <c r="D194" s="11"/>
+      <c r="E194" s="11"/>
+      <c r="F194" s="11"/>
+      <c r="G194" s="11"/>
+      <c r="H194" s="11"/>
       <c r="I194" s="4"/>
       <c r="J194" s="4"/>
       <c r="K194" s="4"/>
@@ -6031,14 +6081,14 @@
       <c r="Z194" s="4"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
-      <c r="A195" s="8"/>
-      <c r="B195" s="9"/>
-      <c r="C195" s="9"/>
-      <c r="D195" s="9"/>
-      <c r="E195" s="9"/>
-      <c r="F195" s="9"/>
-      <c r="G195" s="9"/>
-      <c r="H195" s="9"/>
+      <c r="A195" s="10"/>
+      <c r="B195" s="11"/>
+      <c r="C195" s="11"/>
+      <c r="D195" s="11"/>
+      <c r="E195" s="11"/>
+      <c r="F195" s="11"/>
+      <c r="G195" s="11"/>
+      <c r="H195" s="11"/>
       <c r="I195" s="4"/>
       <c r="J195" s="4"/>
       <c r="K195" s="4"/>
@@ -6059,14 +6109,14 @@
       <c r="Z195" s="4"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
-      <c r="A196" s="8"/>
-      <c r="B196" s="9"/>
-      <c r="C196" s="9"/>
-      <c r="D196" s="9"/>
-      <c r="E196" s="9"/>
-      <c r="F196" s="9"/>
-      <c r="G196" s="9"/>
-      <c r="H196" s="9"/>
+      <c r="A196" s="10"/>
+      <c r="B196" s="11"/>
+      <c r="C196" s="11"/>
+      <c r="D196" s="11"/>
+      <c r="E196" s="11"/>
+      <c r="F196" s="11"/>
+      <c r="G196" s="11"/>
+      <c r="H196" s="11"/>
       <c r="I196" s="4"/>
       <c r="J196" s="4"/>
       <c r="K196" s="4"/>
@@ -6087,14 +6137,14 @@
       <c r="Z196" s="4"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
-      <c r="A197" s="8"/>
-      <c r="B197" s="9"/>
-      <c r="C197" s="9"/>
-      <c r="D197" s="9"/>
-      <c r="E197" s="9"/>
-      <c r="F197" s="9"/>
-      <c r="G197" s="9"/>
-      <c r="H197" s="9"/>
+      <c r="A197" s="10"/>
+      <c r="B197" s="11"/>
+      <c r="C197" s="11"/>
+      <c r="D197" s="11"/>
+      <c r="E197" s="11"/>
+      <c r="F197" s="11"/>
+      <c r="G197" s="11"/>
+      <c r="H197" s="11"/>
       <c r="I197" s="4"/>
       <c r="J197" s="4"/>
       <c r="K197" s="4"/>
@@ -6115,14 +6165,14 @@
       <c r="Z197" s="4"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
-      <c r="A198" s="8"/>
-      <c r="B198" s="9"/>
-      <c r="C198" s="9"/>
-      <c r="D198" s="9"/>
-      <c r="E198" s="9"/>
-      <c r="F198" s="9"/>
-      <c r="G198" s="9"/>
-      <c r="H198" s="9"/>
+      <c r="A198" s="10"/>
+      <c r="B198" s="11"/>
+      <c r="C198" s="11"/>
+      <c r="D198" s="11"/>
+      <c r="E198" s="11"/>
+      <c r="F198" s="11"/>
+      <c r="G198" s="11"/>
+      <c r="H198" s="11"/>
       <c r="I198" s="4"/>
       <c r="J198" s="4"/>
       <c r="K198" s="4"/>
@@ -6143,14 +6193,14 @@
       <c r="Z198" s="4"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
-      <c r="A199" s="8"/>
-      <c r="B199" s="9"/>
-      <c r="C199" s="9"/>
-      <c r="D199" s="9"/>
-      <c r="E199" s="9"/>
-      <c r="F199" s="9"/>
-      <c r="G199" s="9"/>
-      <c r="H199" s="9"/>
+      <c r="A199" s="10"/>
+      <c r="B199" s="11"/>
+      <c r="C199" s="11"/>
+      <c r="D199" s="11"/>
+      <c r="E199" s="11"/>
+      <c r="F199" s="11"/>
+      <c r="G199" s="11"/>
+      <c r="H199" s="11"/>
       <c r="I199" s="4"/>
       <c r="J199" s="4"/>
       <c r="K199" s="4"/>
@@ -6171,14 +6221,14 @@
       <c r="Z199" s="4"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
-      <c r="A200" s="8"/>
-      <c r="B200" s="9"/>
-      <c r="C200" s="9"/>
-      <c r="D200" s="9"/>
-      <c r="E200" s="9"/>
-      <c r="F200" s="9"/>
-      <c r="G200" s="9"/>
-      <c r="H200" s="9"/>
+      <c r="A200" s="10"/>
+      <c r="B200" s="11"/>
+      <c r="C200" s="11"/>
+      <c r="D200" s="11"/>
+      <c r="E200" s="11"/>
+      <c r="F200" s="11"/>
+      <c r="G200" s="11"/>
+      <c r="H200" s="11"/>
       <c r="I200" s="4"/>
       <c r="J200" s="4"/>
       <c r="K200" s="4"/>
@@ -6199,14 +6249,14 @@
       <c r="Z200" s="4"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
-      <c r="A201" s="8"/>
-      <c r="B201" s="9"/>
-      <c r="C201" s="9"/>
-      <c r="D201" s="9"/>
-      <c r="E201" s="9"/>
-      <c r="F201" s="9"/>
-      <c r="G201" s="9"/>
-      <c r="H201" s="9"/>
+      <c r="A201" s="10"/>
+      <c r="B201" s="11"/>
+      <c r="C201" s="11"/>
+      <c r="D201" s="11"/>
+      <c r="E201" s="11"/>
+      <c r="F201" s="11"/>
+      <c r="G201" s="11"/>
+      <c r="H201" s="11"/>
       <c r="I201" s="4"/>
       <c r="J201" s="4"/>
       <c r="K201" s="4"/>
@@ -6227,14 +6277,14 @@
       <c r="Z201" s="4"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
-      <c r="A202" s="8"/>
-      <c r="B202" s="9"/>
-      <c r="C202" s="9"/>
-      <c r="D202" s="9"/>
-      <c r="E202" s="9"/>
-      <c r="F202" s="9"/>
-      <c r="G202" s="9"/>
-      <c r="H202" s="9"/>
+      <c r="A202" s="10"/>
+      <c r="B202" s="11"/>
+      <c r="C202" s="11"/>
+      <c r="D202" s="11"/>
+      <c r="E202" s="11"/>
+      <c r="F202" s="11"/>
+      <c r="G202" s="11"/>
+      <c r="H202" s="11"/>
       <c r="I202" s="4"/>
       <c r="J202" s="4"/>
       <c r="K202" s="4"/>
@@ -6255,14 +6305,14 @@
       <c r="Z202" s="4"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
-      <c r="A203" s="8"/>
-      <c r="B203" s="9"/>
-      <c r="C203" s="9"/>
-      <c r="D203" s="9"/>
-      <c r="E203" s="9"/>
-      <c r="F203" s="9"/>
-      <c r="G203" s="9"/>
-      <c r="H203" s="9"/>
+      <c r="A203" s="10"/>
+      <c r="B203" s="11"/>
+      <c r="C203" s="11"/>
+      <c r="D203" s="11"/>
+      <c r="E203" s="11"/>
+      <c r="F203" s="11"/>
+      <c r="G203" s="11"/>
+      <c r="H203" s="11"/>
       <c r="I203" s="4"/>
       <c r="J203" s="4"/>
       <c r="K203" s="4"/>
@@ -6283,14 +6333,14 @@
       <c r="Z203" s="4"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
-      <c r="A204" s="8"/>
-      <c r="B204" s="9"/>
-      <c r="C204" s="9"/>
-      <c r="D204" s="9"/>
-      <c r="E204" s="9"/>
-      <c r="F204" s="9"/>
-      <c r="G204" s="9"/>
-      <c r="H204" s="9"/>
+      <c r="A204" s="10"/>
+      <c r="B204" s="11"/>
+      <c r="C204" s="11"/>
+      <c r="D204" s="11"/>
+      <c r="E204" s="11"/>
+      <c r="F204" s="11"/>
+      <c r="G204" s="11"/>
+      <c r="H204" s="11"/>
       <c r="I204" s="4"/>
       <c r="J204" s="4"/>
       <c r="K204" s="4"/>
@@ -6311,14 +6361,14 @@
       <c r="Z204" s="4"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
-      <c r="A205" s="8"/>
-      <c r="B205" s="9"/>
-      <c r="C205" s="9"/>
-      <c r="D205" s="9"/>
-      <c r="E205" s="9"/>
-      <c r="F205" s="9"/>
-      <c r="G205" s="9"/>
-      <c r="H205" s="9"/>
+      <c r="A205" s="10"/>
+      <c r="B205" s="11"/>
+      <c r="C205" s="11"/>
+      <c r="D205" s="11"/>
+      <c r="E205" s="11"/>
+      <c r="F205" s="11"/>
+      <c r="G205" s="11"/>
+      <c r="H205" s="11"/>
       <c r="I205" s="4"/>
       <c r="J205" s="4"/>
       <c r="K205" s="4"/>
@@ -6339,14 +6389,14 @@
       <c r="Z205" s="4"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
-      <c r="A206" s="8"/>
-      <c r="B206" s="9"/>
-      <c r="C206" s="9"/>
-      <c r="D206" s="9"/>
-      <c r="E206" s="9"/>
-      <c r="F206" s="9"/>
-      <c r="G206" s="9"/>
-      <c r="H206" s="9"/>
+      <c r="A206" s="10"/>
+      <c r="B206" s="11"/>
+      <c r="C206" s="11"/>
+      <c r="D206" s="11"/>
+      <c r="E206" s="11"/>
+      <c r="F206" s="11"/>
+      <c r="G206" s="11"/>
+      <c r="H206" s="11"/>
       <c r="I206" s="4"/>
       <c r="J206" s="4"/>
       <c r="K206" s="4"/>
@@ -6367,14 +6417,14 @@
       <c r="Z206" s="4"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
-      <c r="A207" s="8"/>
-      <c r="B207" s="9"/>
-      <c r="C207" s="9"/>
-      <c r="D207" s="9"/>
-      <c r="E207" s="9"/>
-      <c r="F207" s="9"/>
-      <c r="G207" s="9"/>
-      <c r="H207" s="9"/>
+      <c r="A207" s="10"/>
+      <c r="B207" s="11"/>
+      <c r="C207" s="11"/>
+      <c r="D207" s="11"/>
+      <c r="E207" s="11"/>
+      <c r="F207" s="11"/>
+      <c r="G207" s="11"/>
+      <c r="H207" s="11"/>
       <c r="I207" s="4"/>
       <c r="J207" s="4"/>
       <c r="K207" s="4"/>
@@ -6395,14 +6445,14 @@
       <c r="Z207" s="4"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
-      <c r="A208" s="8"/>
-      <c r="B208" s="9"/>
-      <c r="C208" s="9"/>
-      <c r="D208" s="9"/>
-      <c r="E208" s="9"/>
-      <c r="F208" s="9"/>
-      <c r="G208" s="9"/>
-      <c r="H208" s="9"/>
+      <c r="A208" s="10"/>
+      <c r="B208" s="11"/>
+      <c r="C208" s="11"/>
+      <c r="D208" s="11"/>
+      <c r="E208" s="11"/>
+      <c r="F208" s="11"/>
+      <c r="G208" s="11"/>
+      <c r="H208" s="11"/>
       <c r="I208" s="4"/>
       <c r="J208" s="4"/>
       <c r="K208" s="4"/>
@@ -6423,14 +6473,14 @@
       <c r="Z208" s="4"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
-      <c r="A209" s="8"/>
-      <c r="B209" s="9"/>
-      <c r="C209" s="9"/>
-      <c r="D209" s="9"/>
-      <c r="E209" s="9"/>
-      <c r="F209" s="9"/>
-      <c r="G209" s="9"/>
-      <c r="H209" s="9"/>
+      <c r="A209" s="10"/>
+      <c r="B209" s="11"/>
+      <c r="C209" s="11"/>
+      <c r="D209" s="11"/>
+      <c r="E209" s="11"/>
+      <c r="F209" s="11"/>
+      <c r="G209" s="11"/>
+      <c r="H209" s="11"/>
       <c r="I209" s="4"/>
       <c r="J209" s="4"/>
       <c r="K209" s="4"/>
@@ -6451,14 +6501,14 @@
       <c r="Z209" s="4"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
-      <c r="A210" s="8"/>
-      <c r="B210" s="9"/>
-      <c r="C210" s="9"/>
-      <c r="D210" s="9"/>
-      <c r="E210" s="9"/>
-      <c r="F210" s="9"/>
-      <c r="G210" s="9"/>
-      <c r="H210" s="9"/>
+      <c r="A210" s="10"/>
+      <c r="B210" s="11"/>
+      <c r="C210" s="11"/>
+      <c r="D210" s="11"/>
+      <c r="E210" s="11"/>
+      <c r="F210" s="11"/>
+      <c r="G210" s="11"/>
+      <c r="H210" s="11"/>
       <c r="I210" s="4"/>
       <c r="J210" s="4"/>
       <c r="K210" s="4"/>
@@ -6479,14 +6529,14 @@
       <c r="Z210" s="4"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
-      <c r="A211" s="8"/>
-      <c r="B211" s="9"/>
-      <c r="C211" s="9"/>
-      <c r="D211" s="9"/>
-      <c r="E211" s="9"/>
-      <c r="F211" s="9"/>
-      <c r="G211" s="9"/>
-      <c r="H211" s="9"/>
+      <c r="A211" s="10"/>
+      <c r="B211" s="11"/>
+      <c r="C211" s="11"/>
+      <c r="D211" s="11"/>
+      <c r="E211" s="11"/>
+      <c r="F211" s="11"/>
+      <c r="G211" s="11"/>
+      <c r="H211" s="11"/>
       <c r="I211" s="4"/>
       <c r="J211" s="4"/>
       <c r="K211" s="4"/>
@@ -6507,14 +6557,14 @@
       <c r="Z211" s="4"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
-      <c r="A212" s="8"/>
-      <c r="B212" s="9"/>
-      <c r="C212" s="9"/>
-      <c r="D212" s="9"/>
-      <c r="E212" s="9"/>
-      <c r="F212" s="9"/>
-      <c r="G212" s="9"/>
-      <c r="H212" s="9"/>
+      <c r="A212" s="10"/>
+      <c r="B212" s="11"/>
+      <c r="C212" s="11"/>
+      <c r="D212" s="11"/>
+      <c r="E212" s="11"/>
+      <c r="F212" s="11"/>
+      <c r="G212" s="11"/>
+      <c r="H212" s="11"/>
       <c r="I212" s="4"/>
       <c r="J212" s="4"/>
       <c r="K212" s="4"/>
@@ -6535,14 +6585,14 @@
       <c r="Z212" s="4"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
-      <c r="A213" s="8"/>
-      <c r="B213" s="9"/>
-      <c r="C213" s="9"/>
-      <c r="D213" s="9"/>
-      <c r="E213" s="9"/>
-      <c r="F213" s="9"/>
-      <c r="G213" s="9"/>
-      <c r="H213" s="9"/>
+      <c r="A213" s="10"/>
+      <c r="B213" s="11"/>
+      <c r="C213" s="11"/>
+      <c r="D213" s="11"/>
+      <c r="E213" s="11"/>
+      <c r="F213" s="11"/>
+      <c r="G213" s="11"/>
+      <c r="H213" s="11"/>
       <c r="I213" s="4"/>
       <c r="J213" s="4"/>
       <c r="K213" s="4"/>
@@ -6563,14 +6613,14 @@
       <c r="Z213" s="4"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
-      <c r="A214" s="8"/>
-      <c r="B214" s="9"/>
-      <c r="C214" s="9"/>
-      <c r="D214" s="9"/>
-      <c r="E214" s="9"/>
-      <c r="F214" s="9"/>
-      <c r="G214" s="9"/>
-      <c r="H214" s="9"/>
+      <c r="A214" s="10"/>
+      <c r="B214" s="11"/>
+      <c r="C214" s="11"/>
+      <c r="D214" s="11"/>
+      <c r="E214" s="11"/>
+      <c r="F214" s="11"/>
+      <c r="G214" s="11"/>
+      <c r="H214" s="11"/>
       <c r="I214" s="4"/>
       <c r="J214" s="4"/>
       <c r="K214" s="4"/>
@@ -6591,14 +6641,14 @@
       <c r="Z214" s="4"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
-      <c r="A215" s="8"/>
-      <c r="B215" s="9"/>
-      <c r="C215" s="9"/>
-      <c r="D215" s="9"/>
-      <c r="E215" s="9"/>
-      <c r="F215" s="9"/>
-      <c r="G215" s="9"/>
-      <c r="H215" s="9"/>
+      <c r="A215" s="10"/>
+      <c r="B215" s="11"/>
+      <c r="C215" s="11"/>
+      <c r="D215" s="11"/>
+      <c r="E215" s="11"/>
+      <c r="F215" s="11"/>
+      <c r="G215" s="11"/>
+      <c r="H215" s="11"/>
       <c r="I215" s="4"/>
       <c r="J215" s="4"/>
       <c r="K215" s="4"/>
@@ -6619,14 +6669,14 @@
       <c r="Z215" s="4"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
-      <c r="A216" s="8"/>
-      <c r="B216" s="9"/>
-      <c r="C216" s="9"/>
-      <c r="D216" s="9"/>
-      <c r="E216" s="9"/>
-      <c r="F216" s="9"/>
-      <c r="G216" s="9"/>
-      <c r="H216" s="9"/>
+      <c r="A216" s="10"/>
+      <c r="B216" s="11"/>
+      <c r="C216" s="11"/>
+      <c r="D216" s="11"/>
+      <c r="E216" s="11"/>
+      <c r="F216" s="11"/>
+      <c r="G216" s="11"/>
+      <c r="H216" s="11"/>
       <c r="I216" s="4"/>
       <c r="J216" s="4"/>
       <c r="K216" s="4"/>
@@ -6647,14 +6697,14 @@
       <c r="Z216" s="4"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
-      <c r="A217" s="8"/>
-      <c r="B217" s="9"/>
-      <c r="C217" s="9"/>
-      <c r="D217" s="9"/>
-      <c r="E217" s="9"/>
-      <c r="F217" s="9"/>
-      <c r="G217" s="9"/>
-      <c r="H217" s="9"/>
+      <c r="A217" s="10"/>
+      <c r="B217" s="11"/>
+      <c r="C217" s="11"/>
+      <c r="D217" s="11"/>
+      <c r="E217" s="11"/>
+      <c r="F217" s="11"/>
+      <c r="G217" s="11"/>
+      <c r="H217" s="11"/>
       <c r="I217" s="4"/>
       <c r="J217" s="4"/>
       <c r="K217" s="4"/>
@@ -6675,14 +6725,14 @@
       <c r="Z217" s="4"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
-      <c r="A218" s="8"/>
-      <c r="B218" s="9"/>
-      <c r="C218" s="9"/>
-      <c r="D218" s="9"/>
-      <c r="E218" s="9"/>
-      <c r="F218" s="9"/>
-      <c r="G218" s="9"/>
-      <c r="H218" s="9"/>
+      <c r="A218" s="10"/>
+      <c r="B218" s="11"/>
+      <c r="C218" s="11"/>
+      <c r="D218" s="11"/>
+      <c r="E218" s="11"/>
+      <c r="F218" s="11"/>
+      <c r="G218" s="11"/>
+      <c r="H218" s="11"/>
       <c r="I218" s="4"/>
       <c r="J218" s="4"/>
       <c r="K218" s="4"/>
@@ -6703,14 +6753,14 @@
       <c r="Z218" s="4"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
-      <c r="A219" s="8"/>
-      <c r="B219" s="9"/>
-      <c r="C219" s="9"/>
-      <c r="D219" s="9"/>
-      <c r="E219" s="9"/>
-      <c r="F219" s="9"/>
-      <c r="G219" s="9"/>
-      <c r="H219" s="9"/>
+      <c r="A219" s="10"/>
+      <c r="B219" s="11"/>
+      <c r="C219" s="11"/>
+      <c r="D219" s="11"/>
+      <c r="E219" s="11"/>
+      <c r="F219" s="11"/>
+      <c r="G219" s="11"/>
+      <c r="H219" s="11"/>
       <c r="I219" s="4"/>
       <c r="J219" s="4"/>
       <c r="K219" s="4"/>
@@ -6731,14 +6781,14 @@
       <c r="Z219" s="4"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
-      <c r="A220" s="8"/>
-      <c r="B220" s="9"/>
-      <c r="C220" s="9"/>
-      <c r="D220" s="9"/>
-      <c r="E220" s="9"/>
-      <c r="F220" s="9"/>
-      <c r="G220" s="9"/>
-      <c r="H220" s="9"/>
+      <c r="A220" s="10"/>
+      <c r="B220" s="11"/>
+      <c r="C220" s="11"/>
+      <c r="D220" s="11"/>
+      <c r="E220" s="11"/>
+      <c r="F220" s="11"/>
+      <c r="G220" s="11"/>
+      <c r="H220" s="11"/>
       <c r="I220" s="4"/>
       <c r="J220" s="4"/>
       <c r="K220" s="4"/>
@@ -28599,22 +28649,22 @@
       <c r="Z1000" s="4"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:J200">
+  <conditionalFormatting sqref="B2:J200 K2:K6">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>AND(ISNUMBER(B2),B2&gt;=90)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:J200">
+  <conditionalFormatting sqref="B2:J200 K2:K6">
     <cfRule type="expression" dxfId="1" priority="2">
       <formula>AND(ISNUMBER(B2),B2&gt;=80,B2&lt;90)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:J200">
+  <conditionalFormatting sqref="B2:J200 K2:K6">
     <cfRule type="expression" dxfId="2" priority="3">
       <formula>AND(ISNUMBER(B2),B2&gt;=70,B2&lt;80)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:J200">
+  <conditionalFormatting sqref="B2:J200 K2:K6">
     <cfRule type="expression" dxfId="3" priority="4">
       <formula>AND(ISNUMBER(B2),B2&lt;70)</formula>
     </cfRule>
